--- a/AAII_Financials/Yearly/GHG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/GHG_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -724,25 +724,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>129400</v>
+        <v>130200</v>
       </c>
       <c r="E8" s="3">
-        <v>166500</v>
+        <v>167700</v>
       </c>
       <c r="F8" s="3">
-        <v>128400</v>
+        <v>129300</v>
       </c>
       <c r="G8" s="3">
-        <v>150800</v>
+        <v>151800</v>
       </c>
       <c r="H8" s="3">
-        <v>125000</v>
+        <v>125900</v>
       </c>
       <c r="I8" s="3">
-        <v>102600</v>
+        <v>103300</v>
       </c>
       <c r="J8" s="3">
-        <v>89400</v>
+        <v>90100</v>
       </c>
       <c r="K8" s="3">
         <v>91200</v>
@@ -823,10 +823,10 @@
         <v>3</v>
       </c>
       <c r="I10" s="3">
-        <v>95600</v>
+        <v>96300</v>
       </c>
       <c r="J10" s="3">
-        <v>80300</v>
+        <v>80800</v>
       </c>
       <c r="K10" s="3">
         <v>79900</v>
@@ -952,7 +952,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>24000</v>
+        <v>24100</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
@@ -994,13 +994,13 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>12800</v>
+        <v>12900</v>
       </c>
       <c r="E15" s="3">
-        <v>12400</v>
+        <v>12500</v>
       </c>
       <c r="F15" s="3">
-        <v>8200</v>
+        <v>8300</v>
       </c>
       <c r="G15" s="3">
         <v>5200</v>
@@ -1051,25 +1051,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>196300</v>
+        <v>197700</v>
       </c>
       <c r="E17" s="3">
-        <v>145300</v>
+        <v>146300</v>
       </c>
       <c r="F17" s="3">
-        <v>84300</v>
+        <v>84900</v>
       </c>
       <c r="G17" s="3">
-        <v>81100</v>
+        <v>81600</v>
       </c>
       <c r="H17" s="3">
-        <v>55300</v>
+        <v>55700</v>
       </c>
       <c r="I17" s="3">
-        <v>51300</v>
+        <v>51700</v>
       </c>
       <c r="J17" s="3">
-        <v>46300</v>
+        <v>46600</v>
       </c>
       <c r="K17" s="3">
         <v>49800</v>
@@ -1093,25 +1093,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-67000</v>
+        <v>-67400</v>
       </c>
       <c r="E18" s="3">
-        <v>21300</v>
+        <v>21400</v>
       </c>
       <c r="F18" s="3">
-        <v>44100</v>
+        <v>44400</v>
       </c>
       <c r="G18" s="3">
-        <v>69700</v>
+        <v>70100</v>
       </c>
       <c r="H18" s="3">
-        <v>69800</v>
+        <v>70200</v>
       </c>
       <c r="I18" s="3">
-        <v>51300</v>
+        <v>51600</v>
       </c>
       <c r="J18" s="3">
-        <v>43100</v>
+        <v>43400</v>
       </c>
       <c r="K18" s="3">
         <v>41300</v>
@@ -1153,16 +1153,16 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>7100</v>
+        <v>7200</v>
       </c>
       <c r="E20" s="3">
-        <v>11200</v>
+        <v>11300</v>
       </c>
       <c r="F20" s="3">
         <v>5300</v>
       </c>
       <c r="G20" s="3">
-        <v>17100</v>
+        <v>17200</v>
       </c>
       <c r="H20" s="3">
         <v>3800</v>
@@ -1171,7 +1171,7 @@
         <v>12000</v>
       </c>
       <c r="J20" s="3">
-        <v>6600</v>
+        <v>6700</v>
       </c>
       <c r="K20" s="3">
         <v>6500</v>
@@ -1195,25 +1195,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-44700</v>
+        <v>-45000</v>
       </c>
       <c r="E21" s="3">
-        <v>46000</v>
+        <v>46300</v>
       </c>
       <c r="F21" s="3">
-        <v>58500</v>
+        <v>58900</v>
       </c>
       <c r="G21" s="3">
-        <v>92400</v>
+        <v>93000</v>
       </c>
       <c r="H21" s="3">
-        <v>77100</v>
+        <v>77600</v>
       </c>
       <c r="I21" s="3">
-        <v>66700</v>
+        <v>67200</v>
       </c>
       <c r="J21" s="3">
-        <v>54600</v>
+        <v>55000</v>
       </c>
       <c r="K21" s="3">
         <v>53800</v>
@@ -1240,7 +1240,7 @@
         <v>3500</v>
       </c>
       <c r="E22" s="3">
-        <v>1700</v>
+        <v>1800</v>
       </c>
       <c r="F22" s="3">
         <v>500</v>
@@ -1279,25 +1279,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-63400</v>
+        <v>-63800</v>
       </c>
       <c r="E23" s="3">
-        <v>30700</v>
+        <v>30900</v>
       </c>
       <c r="F23" s="3">
-        <v>48900</v>
+        <v>49200</v>
       </c>
       <c r="G23" s="3">
-        <v>86400</v>
+        <v>87000</v>
       </c>
       <c r="H23" s="3">
-        <v>73500</v>
+        <v>74000</v>
       </c>
       <c r="I23" s="3">
-        <v>63100</v>
+        <v>63500</v>
       </c>
       <c r="J23" s="3">
-        <v>49700</v>
+        <v>50100</v>
       </c>
       <c r="K23" s="3">
         <v>47800</v>
@@ -1324,22 +1324,22 @@
         <v>-6300</v>
       </c>
       <c r="E24" s="3">
-        <v>15000</v>
+        <v>15100</v>
       </c>
       <c r="F24" s="3">
-        <v>15300</v>
+        <v>15400</v>
       </c>
       <c r="G24" s="3">
-        <v>26200</v>
+        <v>26400</v>
       </c>
       <c r="H24" s="3">
-        <v>21100</v>
+        <v>21200</v>
       </c>
       <c r="I24" s="3">
-        <v>25200</v>
+        <v>25400</v>
       </c>
       <c r="J24" s="3">
-        <v>11600</v>
+        <v>11700</v>
       </c>
       <c r="K24" s="3">
         <v>11500</v>
@@ -1405,25 +1405,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-57100</v>
+        <v>-57500</v>
       </c>
       <c r="E26" s="3">
-        <v>15600</v>
+        <v>15800</v>
       </c>
       <c r="F26" s="3">
-        <v>33700</v>
+        <v>33900</v>
       </c>
       <c r="G26" s="3">
-        <v>60300</v>
+        <v>60700</v>
       </c>
       <c r="H26" s="3">
-        <v>52400</v>
+        <v>52800</v>
       </c>
       <c r="I26" s="3">
-        <v>37800</v>
+        <v>38100</v>
       </c>
       <c r="J26" s="3">
-        <v>38100</v>
+        <v>38400</v>
       </c>
       <c r="K26" s="3">
         <v>36300</v>
@@ -1447,25 +1447,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-52800</v>
+        <v>-53100</v>
       </c>
       <c r="E27" s="3">
-        <v>16200</v>
+        <v>16300</v>
       </c>
       <c r="F27" s="3">
-        <v>36100</v>
+        <v>36300</v>
       </c>
       <c r="G27" s="3">
-        <v>61100</v>
+        <v>61500</v>
       </c>
       <c r="H27" s="3">
-        <v>51300</v>
+        <v>51700</v>
       </c>
       <c r="I27" s="3">
-        <v>37800</v>
+        <v>38000</v>
       </c>
       <c r="J27" s="3">
-        <v>36700</v>
+        <v>37000</v>
       </c>
       <c r="K27" s="3">
         <v>33900</v>
@@ -1657,16 +1657,16 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-7100</v>
+        <v>-7200</v>
       </c>
       <c r="E32" s="3">
-        <v>-11200</v>
+        <v>-11300</v>
       </c>
       <c r="F32" s="3">
         <v>-5300</v>
       </c>
       <c r="G32" s="3">
-        <v>-17100</v>
+        <v>-17200</v>
       </c>
       <c r="H32" s="3">
         <v>-3800</v>
@@ -1675,7 +1675,7 @@
         <v>-12000</v>
       </c>
       <c r="J32" s="3">
-        <v>-6600</v>
+        <v>-6700</v>
       </c>
       <c r="K32" s="3">
         <v>-6500</v>
@@ -1699,25 +1699,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-52800</v>
+        <v>-53100</v>
       </c>
       <c r="E33" s="3">
-        <v>16200</v>
+        <v>16300</v>
       </c>
       <c r="F33" s="3">
-        <v>36100</v>
+        <v>36300</v>
       </c>
       <c r="G33" s="3">
-        <v>61100</v>
+        <v>61500</v>
       </c>
       <c r="H33" s="3">
-        <v>51300</v>
+        <v>51700</v>
       </c>
       <c r="I33" s="3">
-        <v>37800</v>
+        <v>38000</v>
       </c>
       <c r="J33" s="3">
-        <v>36700</v>
+        <v>37000</v>
       </c>
       <c r="K33" s="3">
         <v>33900</v>
@@ -1783,25 +1783,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-52800</v>
+        <v>-53100</v>
       </c>
       <c r="E35" s="3">
-        <v>16200</v>
+        <v>16300</v>
       </c>
       <c r="F35" s="3">
-        <v>36100</v>
+        <v>36300</v>
       </c>
       <c r="G35" s="3">
-        <v>61100</v>
+        <v>61500</v>
       </c>
       <c r="H35" s="3">
-        <v>51300</v>
+        <v>51700</v>
       </c>
       <c r="I35" s="3">
-        <v>37800</v>
+        <v>38000</v>
       </c>
       <c r="J35" s="3">
-        <v>36700</v>
+        <v>37000</v>
       </c>
       <c r="K35" s="3">
         <v>33900</v>
@@ -1908,25 +1908,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>88000</v>
+        <v>88600</v>
       </c>
       <c r="E41" s="3">
-        <v>41200</v>
+        <v>41500</v>
       </c>
       <c r="F41" s="3">
-        <v>84400</v>
+        <v>85000</v>
       </c>
       <c r="G41" s="3">
-        <v>44200</v>
+        <v>44500</v>
       </c>
       <c r="H41" s="3">
-        <v>174500</v>
+        <v>175700</v>
       </c>
       <c r="I41" s="3">
-        <v>22400</v>
+        <v>22500</v>
       </c>
       <c r="J41" s="3">
-        <v>123800</v>
+        <v>124700</v>
       </c>
       <c r="K41" s="3">
         <v>72700</v>
@@ -1950,25 +1950,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>31400</v>
+        <v>31600</v>
       </c>
       <c r="E42" s="3">
-        <v>98800</v>
+        <v>99500</v>
       </c>
       <c r="F42" s="3">
-        <v>75200</v>
+        <v>75700</v>
       </c>
       <c r="G42" s="3">
-        <v>89000</v>
+        <v>89600</v>
       </c>
       <c r="H42" s="3">
-        <v>137100</v>
+        <v>138100</v>
       </c>
       <c r="I42" s="3">
-        <v>150500</v>
+        <v>151500</v>
       </c>
       <c r="J42" s="3">
-        <v>37800</v>
+        <v>38000</v>
       </c>
       <c r="K42" s="3">
         <v>57200</v>
@@ -1992,25 +1992,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>102100</v>
+        <v>102800</v>
       </c>
       <c r="E43" s="3">
-        <v>97100</v>
+        <v>97700</v>
       </c>
       <c r="F43" s="3">
-        <v>46100</v>
+        <v>46400</v>
       </c>
       <c r="G43" s="3">
-        <v>29500</v>
+        <v>29700</v>
       </c>
       <c r="H43" s="3">
-        <v>27200</v>
+        <v>27400</v>
       </c>
       <c r="I43" s="3">
-        <v>8800</v>
+        <v>8900</v>
       </c>
       <c r="J43" s="3">
-        <v>25700</v>
+        <v>25800</v>
       </c>
       <c r="K43" s="3">
         <v>17100</v>
@@ -2076,25 +2076,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>13200</v>
+        <v>13300</v>
       </c>
       <c r="E45" s="3">
-        <v>15500</v>
+        <v>15600</v>
       </c>
       <c r="F45" s="3">
-        <v>12600</v>
+        <v>12700</v>
       </c>
       <c r="G45" s="3">
-        <v>11700</v>
+        <v>11800</v>
       </c>
       <c r="H45" s="3">
         <v>8100</v>
       </c>
       <c r="I45" s="3">
-        <v>23200</v>
+        <v>23300</v>
       </c>
       <c r="J45" s="3">
-        <v>33600</v>
+        <v>33800</v>
       </c>
       <c r="K45" s="3">
         <v>15200</v>
@@ -2118,25 +2118,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>235000</v>
+        <v>236600</v>
       </c>
       <c r="E46" s="3">
-        <v>252900</v>
+        <v>254600</v>
       </c>
       <c r="F46" s="3">
-        <v>218800</v>
+        <v>220200</v>
       </c>
       <c r="G46" s="3">
-        <v>174700</v>
+        <v>175900</v>
       </c>
       <c r="H46" s="3">
-        <v>338400</v>
+        <v>340700</v>
       </c>
       <c r="I46" s="3">
-        <v>205100</v>
+        <v>206500</v>
       </c>
       <c r="J46" s="3">
-        <v>221100</v>
+        <v>222600</v>
       </c>
       <c r="K46" s="3">
         <v>162500</v>
@@ -2160,22 +2160,22 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>83300</v>
+        <v>83800</v>
       </c>
       <c r="E47" s="3">
-        <v>89100</v>
+        <v>89700</v>
       </c>
       <c r="F47" s="3">
-        <v>143500</v>
+        <v>144400</v>
       </c>
       <c r="G47" s="3">
-        <v>149200</v>
+        <v>150200</v>
       </c>
       <c r="H47" s="3">
-        <v>59100</v>
+        <v>59500</v>
       </c>
       <c r="I47" s="3">
-        <v>17300</v>
+        <v>17400</v>
       </c>
       <c r="J47" s="3">
         <v>4900</v>
@@ -2202,25 +2202,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>328600</v>
+        <v>330800</v>
       </c>
       <c r="E48" s="3">
-        <v>144300</v>
+        <v>145300</v>
       </c>
       <c r="F48" s="3">
-        <v>92300</v>
+        <v>92900</v>
       </c>
       <c r="G48" s="3">
-        <v>84900</v>
+        <v>85500</v>
       </c>
       <c r="H48" s="3">
-        <v>61400</v>
+        <v>61800</v>
       </c>
       <c r="I48" s="3">
-        <v>13300</v>
+        <v>13400</v>
       </c>
       <c r="J48" s="3">
-        <v>15200</v>
+        <v>15400</v>
       </c>
       <c r="K48" s="3">
         <v>20300</v>
@@ -2244,19 +2244,19 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>9300</v>
+        <v>9400</v>
       </c>
       <c r="E49" s="3">
-        <v>88500</v>
+        <v>89100</v>
       </c>
       <c r="F49" s="3">
-        <v>81700</v>
+        <v>82300</v>
       </c>
       <c r="G49" s="3">
-        <v>82300</v>
+        <v>82900</v>
       </c>
       <c r="H49" s="3">
-        <v>8300</v>
+        <v>8400</v>
       </c>
       <c r="I49" s="3">
         <v>900</v>
@@ -2370,25 +2370,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>47500</v>
+        <v>47800</v>
       </c>
       <c r="E52" s="3">
-        <v>69600</v>
+        <v>70100</v>
       </c>
       <c r="F52" s="3">
-        <v>29200</v>
+        <v>29400</v>
       </c>
       <c r="G52" s="3">
-        <v>35900</v>
+        <v>36100</v>
       </c>
       <c r="H52" s="3">
-        <v>22400</v>
+        <v>22600</v>
       </c>
       <c r="I52" s="3">
-        <v>5800</v>
+        <v>5900</v>
       </c>
       <c r="J52" s="3">
-        <v>16600</v>
+        <v>16800</v>
       </c>
       <c r="K52" s="3">
         <v>6300</v>
@@ -2454,25 +2454,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>703700</v>
+        <v>708500</v>
       </c>
       <c r="E54" s="3">
-        <v>644400</v>
+        <v>648800</v>
       </c>
       <c r="F54" s="3">
-        <v>565400</v>
+        <v>569300</v>
       </c>
       <c r="G54" s="3">
-        <v>527000</v>
+        <v>530600</v>
       </c>
       <c r="H54" s="3">
-        <v>425300</v>
+        <v>428200</v>
       </c>
       <c r="I54" s="3">
-        <v>242500</v>
+        <v>244100</v>
       </c>
       <c r="J54" s="3">
-        <v>259000</v>
+        <v>260800</v>
       </c>
       <c r="K54" s="3">
         <v>202100</v>
@@ -2574,19 +2574,19 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>33400</v>
+        <v>33600</v>
       </c>
       <c r="E58" s="3">
-        <v>56100</v>
+        <v>56500</v>
       </c>
       <c r="F58" s="3">
-        <v>20700</v>
+        <v>20900</v>
       </c>
       <c r="G58" s="3">
         <v>8300</v>
       </c>
       <c r="H58" s="3">
-        <v>16600</v>
+        <v>16700</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>3</v>
@@ -2616,25 +2616,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>134300</v>
+        <v>135200</v>
       </c>
       <c r="E59" s="3">
-        <v>113200</v>
+        <v>114000</v>
       </c>
       <c r="F59" s="3">
-        <v>96600</v>
+        <v>97300</v>
       </c>
       <c r="G59" s="3">
-        <v>99400</v>
+        <v>100100</v>
       </c>
       <c r="H59" s="3">
-        <v>178700</v>
+        <v>179900</v>
       </c>
       <c r="I59" s="3">
-        <v>90500</v>
+        <v>91200</v>
       </c>
       <c r="J59" s="3">
-        <v>66800</v>
+        <v>67300</v>
       </c>
       <c r="K59" s="3">
         <v>51500</v>
@@ -2658,25 +2658,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>170500</v>
+        <v>171700</v>
       </c>
       <c r="E60" s="3">
-        <v>172600</v>
+        <v>173800</v>
       </c>
       <c r="F60" s="3">
-        <v>120100</v>
+        <v>120900</v>
       </c>
       <c r="G60" s="3">
-        <v>109800</v>
+        <v>110500</v>
       </c>
       <c r="H60" s="3">
-        <v>98000</v>
+        <v>98700</v>
       </c>
       <c r="I60" s="3">
-        <v>91600</v>
+        <v>92200</v>
       </c>
       <c r="J60" s="3">
-        <v>67900</v>
+        <v>68300</v>
       </c>
       <c r="K60" s="3">
         <v>52500</v>
@@ -2700,10 +2700,10 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>22100</v>
+        <v>22200</v>
       </c>
       <c r="E61" s="3">
-        <v>41700</v>
+        <v>42000</v>
       </c>
       <c r="F61" s="3">
         <v>0</v>
@@ -2742,25 +2742,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>305500</v>
+        <v>307600</v>
       </c>
       <c r="E62" s="3">
-        <v>148100</v>
+        <v>149100</v>
       </c>
       <c r="F62" s="3">
-        <v>134700</v>
+        <v>135600</v>
       </c>
       <c r="G62" s="3">
-        <v>138600</v>
+        <v>139500</v>
       </c>
       <c r="H62" s="3">
-        <v>149600</v>
+        <v>150600</v>
       </c>
       <c r="I62" s="3">
-        <v>49800</v>
+        <v>50100</v>
       </c>
       <c r="J62" s="3">
-        <v>49300</v>
+        <v>49700</v>
       </c>
       <c r="K62" s="3">
         <v>37900</v>
@@ -2910,25 +2910,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>504200</v>
+        <v>507700</v>
       </c>
       <c r="E66" s="3">
-        <v>387900</v>
+        <v>390600</v>
       </c>
       <c r="F66" s="3">
-        <v>275000</v>
+        <v>276900</v>
       </c>
       <c r="G66" s="3">
-        <v>270000</v>
+        <v>271800</v>
       </c>
       <c r="H66" s="3">
-        <v>197300</v>
+        <v>198600</v>
       </c>
       <c r="I66" s="3">
-        <v>141400</v>
+        <v>142300</v>
       </c>
       <c r="J66" s="3">
-        <v>117300</v>
+        <v>118100</v>
       </c>
       <c r="K66" s="3">
         <v>90600</v>
@@ -3138,25 +3138,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-7700</v>
+        <v>-7800</v>
       </c>
       <c r="E72" s="3">
-        <v>45100</v>
+        <v>45400</v>
       </c>
       <c r="F72" s="3">
-        <v>78700</v>
+        <v>79200</v>
       </c>
       <c r="G72" s="3">
-        <v>42600</v>
+        <v>42900</v>
       </c>
       <c r="H72" s="3">
-        <v>34900</v>
+        <v>35100</v>
       </c>
       <c r="I72" s="3">
-        <v>30800</v>
+        <v>31000</v>
       </c>
       <c r="J72" s="3">
-        <v>76800</v>
+        <v>77400</v>
       </c>
       <c r="K72" s="3">
         <v>44300</v>
@@ -3306,25 +3306,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>199400</v>
+        <v>200800</v>
       </c>
       <c r="E76" s="3">
-        <v>256500</v>
+        <v>258300</v>
       </c>
       <c r="F76" s="3">
-        <v>290400</v>
+        <v>292400</v>
       </c>
       <c r="G76" s="3">
-        <v>257000</v>
+        <v>258700</v>
       </c>
       <c r="H76" s="3">
-        <v>228000</v>
+        <v>229500</v>
       </c>
       <c r="I76" s="3">
-        <v>101100</v>
+        <v>101800</v>
       </c>
       <c r="J76" s="3">
-        <v>141700</v>
+        <v>142700</v>
       </c>
       <c r="K76" s="3">
         <v>111500</v>
@@ -3437,25 +3437,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-52800</v>
+        <v>-53100</v>
       </c>
       <c r="E81" s="3">
-        <v>16200</v>
+        <v>16300</v>
       </c>
       <c r="F81" s="3">
-        <v>36100</v>
+        <v>36300</v>
       </c>
       <c r="G81" s="3">
-        <v>61100</v>
+        <v>61500</v>
       </c>
       <c r="H81" s="3">
-        <v>51300</v>
+        <v>51700</v>
       </c>
       <c r="I81" s="3">
-        <v>37800</v>
+        <v>38000</v>
       </c>
       <c r="J81" s="3">
-        <v>36700</v>
+        <v>37000</v>
       </c>
       <c r="K81" s="3">
         <v>33900</v>
@@ -3497,22 +3497,22 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>15200</v>
+        <v>15300</v>
       </c>
       <c r="E83" s="3">
-        <v>13500</v>
+        <v>13600</v>
       </c>
       <c r="F83" s="3">
-        <v>9100</v>
+        <v>9200</v>
       </c>
       <c r="G83" s="3">
         <v>5600</v>
       </c>
       <c r="H83" s="3">
+        <v>3600</v>
+      </c>
+      <c r="I83" s="3">
         <v>3500</v>
-      </c>
-      <c r="I83" s="3">
-        <v>3400</v>
       </c>
       <c r="J83" s="3">
         <v>4900</v>
@@ -3749,25 +3749,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>40300</v>
+        <v>40600</v>
       </c>
       <c r="E89" s="3">
-        <v>49800</v>
+        <v>50200</v>
       </c>
       <c r="F89" s="3">
-        <v>40800</v>
+        <v>41000</v>
       </c>
       <c r="G89" s="3">
-        <v>71000</v>
+        <v>71400</v>
       </c>
       <c r="H89" s="3">
-        <v>76600</v>
+        <v>77100</v>
       </c>
       <c r="I89" s="3">
-        <v>64800</v>
+        <v>65300</v>
       </c>
       <c r="J89" s="3">
-        <v>61200</v>
+        <v>61700</v>
       </c>
       <c r="K89" s="3">
         <v>51300</v>
@@ -3809,19 +3809,19 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-9500</v>
+        <v>-9600</v>
       </c>
       <c r="E91" s="3">
-        <v>-77500</v>
+        <v>-78000</v>
       </c>
       <c r="F91" s="3">
-        <v>-15500</v>
+        <v>-15600</v>
       </c>
       <c r="G91" s="3">
-        <v>-29500</v>
+        <v>-29700</v>
       </c>
       <c r="H91" s="3">
-        <v>-19100</v>
+        <v>-19300</v>
       </c>
       <c r="I91" s="3">
         <v>-2300</v>
@@ -3935,25 +3935,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>55000</v>
+        <v>55400</v>
       </c>
       <c r="E94" s="3">
-        <v>-128200</v>
+        <v>-129100</v>
       </c>
       <c r="F94" s="3">
-        <v>-15400</v>
+        <v>-15500</v>
       </c>
       <c r="G94" s="3">
-        <v>-168500</v>
+        <v>-169600</v>
       </c>
       <c r="H94" s="3">
-        <v>-25100</v>
+        <v>-25300</v>
       </c>
       <c r="I94" s="3">
-        <v>-102800</v>
+        <v>-103500</v>
       </c>
       <c r="J94" s="3">
-        <v>10200</v>
+        <v>10300</v>
       </c>
       <c r="K94" s="3">
         <v>-26800</v>
@@ -3998,16 +3998,16 @@
         <v>-5700</v>
       </c>
       <c r="E96" s="3">
-        <v>-44200</v>
+        <v>-44500</v>
       </c>
       <c r="F96" s="3">
         <v>0</v>
       </c>
       <c r="G96" s="3">
-        <v>-31300</v>
+        <v>-31600</v>
       </c>
       <c r="H96" s="3">
-        <v>-27700</v>
+        <v>-27900</v>
       </c>
       <c r="I96" s="3">
         <v>0</v>
@@ -4163,25 +4163,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-47200</v>
+        <v>-47500</v>
       </c>
       <c r="E100" s="3">
-        <v>35300</v>
+        <v>35500</v>
       </c>
       <c r="F100" s="3">
-        <v>16000</v>
+        <v>16100</v>
       </c>
       <c r="G100" s="3">
-        <v>-29300</v>
+        <v>-29500</v>
       </c>
       <c r="H100" s="3">
-        <v>91600</v>
+        <v>92200</v>
       </c>
       <c r="I100" s="3">
-        <v>-89100</v>
+        <v>-89700</v>
       </c>
       <c r="J100" s="3">
-        <v>-18400</v>
+        <v>-18500</v>
       </c>
       <c r="K100" s="3">
         <v>-7400</v>
@@ -4217,7 +4217,7 @@
         <v>-1000</v>
       </c>
       <c r="H101" s="3">
-        <v>9100</v>
+        <v>9200</v>
       </c>
       <c r="I101" s="3">
         <v>-200</v>
@@ -4247,25 +4247,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>48300</v>
+        <v>48600</v>
       </c>
       <c r="E102" s="3">
-        <v>-43200</v>
+        <v>-43500</v>
       </c>
       <c r="F102" s="3">
-        <v>40300</v>
+        <v>40500</v>
       </c>
       <c r="G102" s="3">
-        <v>-127700</v>
+        <v>-128600</v>
       </c>
       <c r="H102" s="3">
-        <v>152200</v>
+        <v>153300</v>
       </c>
       <c r="I102" s="3">
-        <v>-127300</v>
+        <v>-128200</v>
       </c>
       <c r="J102" s="3">
-        <v>54000</v>
+        <v>54300</v>
       </c>
       <c r="K102" s="3">
         <v>17900</v>

--- a/AAII_Financials/Yearly/GHG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/GHG_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="92">
   <si>
     <t>GHG</t>
   </si>
@@ -656,58 +656,58 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
@@ -717,39 +717,42 @@
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>130200</v>
+        <v>224800</v>
       </c>
       <c r="E8" s="3">
-        <v>167700</v>
+        <v>203000</v>
       </c>
       <c r="F8" s="3">
-        <v>129300</v>
+        <v>271900</v>
       </c>
       <c r="G8" s="3">
-        <v>151800</v>
+        <v>128500</v>
       </c>
       <c r="H8" s="3">
-        <v>125900</v>
+        <v>150800</v>
       </c>
       <c r="I8" s="3">
-        <v>103300</v>
+        <v>125100</v>
       </c>
       <c r="J8" s="3">
+        <v>102700</v>
+      </c>
+      <c r="K8" s="3">
         <v>90100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>91200</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
@@ -759,9 +762,12 @@
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -780,18 +786,18 @@
       <c r="H9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I9" s="3">
+      <c r="I9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J9" s="3">
         <v>7000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>9200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>11300</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
@@ -801,9 +807,12 @@
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -822,18 +831,18 @@
       <c r="H10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I10" s="3">
-        <v>96300</v>
+      <c r="I10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J10" s="3">
+        <v>95700</v>
+      </c>
+      <c r="K10" s="3">
         <v>80800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>79900</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
@@ -843,9 +852,12 @@
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -862,8 +874,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -903,9 +916,12 @@
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -945,20 +961,23 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>24100</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>24000</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
@@ -966,18 +985,18 @@
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J14" s="3">
         <v>0</v>
       </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>1000</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
@@ -987,39 +1006,42 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>12900</v>
+        <v>12800</v>
       </c>
       <c r="E15" s="3">
-        <v>12500</v>
+        <v>14400</v>
       </c>
       <c r="F15" s="3">
+        <v>14900</v>
+      </c>
+      <c r="G15" s="3">
         <v>8300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>5200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>3300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>200</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1029,9 +1051,12 @@
       <c r="O15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1045,38 +1070,39 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>197700</v>
+        <v>178400</v>
       </c>
       <c r="E17" s="3">
-        <v>146300</v>
+        <v>276000</v>
       </c>
       <c r="F17" s="3">
-        <v>84900</v>
+        <v>254000</v>
       </c>
       <c r="G17" s="3">
-        <v>81600</v>
+        <v>84400</v>
       </c>
       <c r="H17" s="3">
-        <v>55700</v>
+        <v>81100</v>
       </c>
       <c r="I17" s="3">
-        <v>51700</v>
+        <v>55300</v>
       </c>
       <c r="J17" s="3">
+        <v>51400</v>
+      </c>
+      <c r="K17" s="3">
         <v>46600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>49800</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1086,39 +1112,42 @@
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-67400</v>
+        <v>46400</v>
       </c>
       <c r="E18" s="3">
-        <v>21400</v>
+        <v>-73000</v>
       </c>
       <c r="F18" s="3">
-        <v>44400</v>
+        <v>17900</v>
       </c>
       <c r="G18" s="3">
-        <v>70100</v>
+        <v>44100</v>
       </c>
       <c r="H18" s="3">
-        <v>70200</v>
+        <v>69700</v>
       </c>
       <c r="I18" s="3">
-        <v>51600</v>
+        <v>69800</v>
       </c>
       <c r="J18" s="3">
+        <v>51300</v>
+      </c>
+      <c r="K18" s="3">
         <v>43400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>41300</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1128,9 +1157,12 @@
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1147,38 +1179,39 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E20" s="3">
         <v>7200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>11300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>5300</v>
       </c>
-      <c r="G20" s="3">
-        <v>17200</v>
-      </c>
       <c r="H20" s="3">
+        <v>17100</v>
+      </c>
+      <c r="I20" s="3">
         <v>3800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>12000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>6700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>6500</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1188,39 +1221,42 @@
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-45000</v>
+        <v>70600</v>
       </c>
       <c r="E21" s="3">
-        <v>46300</v>
+        <v>-48500</v>
       </c>
       <c r="F21" s="3">
-        <v>58900</v>
+        <v>45600</v>
       </c>
       <c r="G21" s="3">
-        <v>93000</v>
+        <v>58500</v>
       </c>
       <c r="H21" s="3">
-        <v>77600</v>
+        <v>92400</v>
       </c>
       <c r="I21" s="3">
-        <v>67200</v>
+        <v>77100</v>
       </c>
       <c r="J21" s="3">
+        <v>66700</v>
+      </c>
+      <c r="K21" s="3">
         <v>55000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>53800</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1230,38 +1266,41 @@
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>3500</v>
+        <v>1900</v>
       </c>
       <c r="E22" s="3">
-        <v>1800</v>
+        <v>3900</v>
       </c>
       <c r="F22" s="3">
+        <v>2100</v>
+      </c>
+      <c r="G22" s="3">
         <v>500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>200</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
       <c r="K22" s="3">
         <v>0</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
+      <c r="L22" s="3">
+        <v>0</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>3</v>
@@ -1272,39 +1311,42 @@
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-63800</v>
+        <v>52600</v>
       </c>
       <c r="E23" s="3">
-        <v>30900</v>
+        <v>-69700</v>
       </c>
       <c r="F23" s="3">
-        <v>49200</v>
+        <v>27000</v>
       </c>
       <c r="G23" s="3">
-        <v>87000</v>
+        <v>48900</v>
       </c>
       <c r="H23" s="3">
-        <v>74000</v>
+        <v>86500</v>
       </c>
       <c r="I23" s="3">
-        <v>63500</v>
+        <v>73500</v>
       </c>
       <c r="J23" s="3">
+        <v>63100</v>
+      </c>
+      <c r="K23" s="3">
         <v>50100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>47800</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1314,39 +1356,42 @@
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-6300</v>
+        <v>16400</v>
       </c>
       <c r="E24" s="3">
-        <v>15100</v>
+        <v>-6100</v>
       </c>
       <c r="F24" s="3">
-        <v>15400</v>
+        <v>15500</v>
       </c>
       <c r="G24" s="3">
-        <v>26400</v>
+        <v>15300</v>
       </c>
       <c r="H24" s="3">
-        <v>21200</v>
+        <v>26200</v>
       </c>
       <c r="I24" s="3">
-        <v>25400</v>
+        <v>21100</v>
       </c>
       <c r="J24" s="3">
+        <v>25200</v>
+      </c>
+      <c r="K24" s="3">
         <v>11700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>11500</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1356,9 +1401,12 @@
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1398,39 +1446,42 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-57500</v>
+        <v>36200</v>
       </c>
       <c r="E26" s="3">
-        <v>15800</v>
+        <v>-63600</v>
       </c>
       <c r="F26" s="3">
-        <v>33900</v>
+        <v>11500</v>
       </c>
       <c r="G26" s="3">
-        <v>60700</v>
+        <v>33700</v>
       </c>
       <c r="H26" s="3">
-        <v>52800</v>
+        <v>60300</v>
       </c>
       <c r="I26" s="3">
-        <v>38100</v>
+        <v>52400</v>
       </c>
       <c r="J26" s="3">
+        <v>37900</v>
+      </c>
+      <c r="K26" s="3">
         <v>38400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>36300</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1440,39 +1491,42 @@
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-53100</v>
+        <v>37200</v>
       </c>
       <c r="E27" s="3">
-        <v>16300</v>
+        <v>-58700</v>
       </c>
       <c r="F27" s="3">
-        <v>36300</v>
+        <v>12300</v>
       </c>
       <c r="G27" s="3">
-        <v>61500</v>
+        <v>36100</v>
       </c>
       <c r="H27" s="3">
-        <v>51700</v>
+        <v>61200</v>
       </c>
       <c r="I27" s="3">
-        <v>38000</v>
+        <v>51400</v>
       </c>
       <c r="J27" s="3">
+        <v>37800</v>
+      </c>
+      <c r="K27" s="3">
         <v>37000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>33900</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1482,9 +1536,12 @@
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1524,9 +1581,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1566,9 +1626,12 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1608,9 +1671,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1650,39 +1716,42 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-7200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-11300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-5300</v>
       </c>
-      <c r="G32" s="3">
-        <v>-17200</v>
-      </c>
       <c r="H32" s="3">
+        <v>-17100</v>
+      </c>
+      <c r="I32" s="3">
         <v>-3800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-12000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-6700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-6500</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1692,39 +1761,42 @@
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-53100</v>
+        <v>37200</v>
       </c>
       <c r="E33" s="3">
-        <v>16300</v>
+        <v>-58700</v>
       </c>
       <c r="F33" s="3">
-        <v>36300</v>
+        <v>12300</v>
       </c>
       <c r="G33" s="3">
-        <v>61500</v>
+        <v>36100</v>
       </c>
       <c r="H33" s="3">
-        <v>51700</v>
+        <v>61200</v>
       </c>
       <c r="I33" s="3">
-        <v>38000</v>
+        <v>51400</v>
       </c>
       <c r="J33" s="3">
+        <v>37800</v>
+      </c>
+      <c r="K33" s="3">
         <v>37000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>33900</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1734,9 +1806,12 @@
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1776,39 +1851,42 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-53100</v>
+        <v>37200</v>
       </c>
       <c r="E35" s="3">
-        <v>16300</v>
+        <v>-58700</v>
       </c>
       <c r="F35" s="3">
-        <v>36300</v>
+        <v>12300</v>
       </c>
       <c r="G35" s="3">
-        <v>61500</v>
+        <v>36100</v>
       </c>
       <c r="H35" s="3">
-        <v>51700</v>
+        <v>61200</v>
       </c>
       <c r="I35" s="3">
-        <v>38000</v>
+        <v>51400</v>
       </c>
       <c r="J35" s="3">
+        <v>37800</v>
+      </c>
+      <c r="K35" s="3">
         <v>37000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>33900</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1818,44 +1896,47 @@
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1865,9 +1946,12 @@
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1884,8 +1968,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1902,38 +1987,39 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>88600</v>
+        <v>105800</v>
       </c>
       <c r="E41" s="3">
-        <v>41500</v>
+        <v>96600</v>
       </c>
       <c r="F41" s="3">
-        <v>85000</v>
+        <v>41200</v>
       </c>
       <c r="G41" s="3">
-        <v>44500</v>
+        <v>84500</v>
       </c>
       <c r="H41" s="3">
-        <v>175700</v>
+        <v>44200</v>
       </c>
       <c r="I41" s="3">
-        <v>22500</v>
+        <v>174600</v>
       </c>
       <c r="J41" s="3">
+        <v>22400</v>
+      </c>
+      <c r="K41" s="3">
         <v>124700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>72700</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1943,39 +2029,42 @@
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>31600</v>
+        <v>61300</v>
       </c>
       <c r="E42" s="3">
-        <v>99500</v>
+        <v>31400</v>
       </c>
       <c r="F42" s="3">
-        <v>75700</v>
+        <v>98800</v>
       </c>
       <c r="G42" s="3">
-        <v>89600</v>
+        <v>75200</v>
       </c>
       <c r="H42" s="3">
-        <v>138100</v>
+        <v>89000</v>
       </c>
       <c r="I42" s="3">
-        <v>151500</v>
+        <v>137200</v>
       </c>
       <c r="J42" s="3">
+        <v>150500</v>
+      </c>
+      <c r="K42" s="3">
         <v>38000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>57200</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
@@ -1985,39 +2074,42 @@
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>102800</v>
+        <v>39700</v>
       </c>
       <c r="E43" s="3">
-        <v>97700</v>
+        <v>103200</v>
       </c>
       <c r="F43" s="3">
-        <v>46400</v>
+        <v>97100</v>
       </c>
       <c r="G43" s="3">
-        <v>29700</v>
+        <v>46100</v>
       </c>
       <c r="H43" s="3">
-        <v>27400</v>
+        <v>29500</v>
       </c>
       <c r="I43" s="3">
-        <v>8900</v>
+        <v>27200</v>
       </c>
       <c r="J43" s="3">
+        <v>8800</v>
+      </c>
+      <c r="K43" s="3">
         <v>25800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>17100</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2027,29 +2119,32 @@
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E44" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F44" s="3">
         <v>300</v>
       </c>
-      <c r="E44" s="3">
-        <v>300</v>
-      </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>500</v>
-      </c>
-      <c r="G44" s="3">
-        <v>400</v>
       </c>
       <c r="H44" s="3">
         <v>400</v>
       </c>
       <c r="I44" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="J44" s="3">
         <v>300</v>
@@ -2057,8 +2152,8 @@
       <c r="K44" s="3">
         <v>300</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>3</v>
+      <c r="L44" s="3">
+        <v>300</v>
       </c>
       <c r="M44" s="3" t="s">
         <v>3</v>
@@ -2069,39 +2164,42 @@
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>13300</v>
+        <v>15200</v>
       </c>
       <c r="E45" s="3">
-        <v>15600</v>
+        <v>16400</v>
       </c>
       <c r="F45" s="3">
-        <v>12700</v>
+        <v>15500</v>
       </c>
       <c r="G45" s="3">
-        <v>11800</v>
+        <v>12600</v>
       </c>
       <c r="H45" s="3">
+        <v>11700</v>
+      </c>
+      <c r="I45" s="3">
         <v>8100</v>
       </c>
-      <c r="I45" s="3">
-        <v>23300</v>
-      </c>
       <c r="J45" s="3">
+        <v>23200</v>
+      </c>
+      <c r="K45" s="3">
         <v>33800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>15200</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2111,39 +2209,42 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>236600</v>
+        <v>224800</v>
       </c>
       <c r="E46" s="3">
-        <v>254600</v>
+        <v>250700</v>
       </c>
       <c r="F46" s="3">
-        <v>220200</v>
+        <v>253000</v>
       </c>
       <c r="G46" s="3">
-        <v>175900</v>
+        <v>218900</v>
       </c>
       <c r="H46" s="3">
-        <v>340700</v>
+        <v>174800</v>
       </c>
       <c r="I46" s="3">
-        <v>206500</v>
+        <v>338600</v>
       </c>
       <c r="J46" s="3">
+        <v>205200</v>
+      </c>
+      <c r="K46" s="3">
         <v>222600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>162500</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2153,39 +2254,42 @@
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>83800</v>
+        <v>61100</v>
       </c>
       <c r="E47" s="3">
-        <v>89700</v>
+        <v>83100</v>
       </c>
       <c r="F47" s="3">
-        <v>144400</v>
+        <v>89200</v>
       </c>
       <c r="G47" s="3">
-        <v>150200</v>
+        <v>143500</v>
       </c>
       <c r="H47" s="3">
-        <v>59500</v>
+        <v>149200</v>
       </c>
       <c r="I47" s="3">
-        <v>17400</v>
+        <v>59100</v>
       </c>
       <c r="J47" s="3">
+        <v>17300</v>
+      </c>
+      <c r="K47" s="3">
         <v>4900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>11700</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2195,39 +2299,42 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>330800</v>
+        <v>324700</v>
       </c>
       <c r="E48" s="3">
-        <v>145300</v>
+        <v>353400</v>
       </c>
       <c r="F48" s="3">
-        <v>92900</v>
+        <v>144400</v>
       </c>
       <c r="G48" s="3">
-        <v>85500</v>
+        <v>92400</v>
       </c>
       <c r="H48" s="3">
-        <v>61800</v>
+        <v>85000</v>
       </c>
       <c r="I48" s="3">
+        <v>61500</v>
+      </c>
+      <c r="J48" s="3">
         <v>13400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>15400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>20300</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2237,39 +2344,42 @@
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>9400</v>
+        <v>40700</v>
       </c>
       <c r="E49" s="3">
-        <v>89100</v>
+        <v>43200</v>
       </c>
       <c r="F49" s="3">
-        <v>82300</v>
+        <v>88600</v>
       </c>
       <c r="G49" s="3">
-        <v>82900</v>
+        <v>81800</v>
       </c>
       <c r="H49" s="3">
-        <v>8400</v>
+        <v>82400</v>
       </c>
       <c r="I49" s="3">
+        <v>8300</v>
+      </c>
+      <c r="J49" s="3">
         <v>900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1300</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2279,9 +2389,12 @@
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2321,9 +2434,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2363,39 +2479,42 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>47800</v>
+        <v>48700</v>
       </c>
       <c r="E52" s="3">
-        <v>70100</v>
+        <v>51600</v>
       </c>
       <c r="F52" s="3">
-        <v>29400</v>
+        <v>69600</v>
       </c>
       <c r="G52" s="3">
-        <v>36100</v>
+        <v>29200</v>
       </c>
       <c r="H52" s="3">
-        <v>22600</v>
+        <v>35900</v>
       </c>
       <c r="I52" s="3">
-        <v>5900</v>
+        <v>22400</v>
       </c>
       <c r="J52" s="3">
+        <v>5800</v>
+      </c>
+      <c r="K52" s="3">
         <v>16800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>6300</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2405,9 +2524,12 @@
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2447,39 +2569,42 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>708500</v>
+        <v>700000</v>
       </c>
       <c r="E54" s="3">
-        <v>648800</v>
+        <v>785300</v>
       </c>
       <c r="F54" s="3">
-        <v>569300</v>
+        <v>644800</v>
       </c>
       <c r="G54" s="3">
-        <v>530600</v>
+        <v>565800</v>
       </c>
       <c r="H54" s="3">
-        <v>428200</v>
+        <v>527300</v>
       </c>
       <c r="I54" s="3">
-        <v>244100</v>
+        <v>425500</v>
       </c>
       <c r="J54" s="3">
+        <v>242600</v>
+      </c>
+      <c r="K54" s="3">
         <v>260800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>202100</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2489,9 +2614,12 @@
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2508,8 +2636,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2526,37 +2655,38 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2900</v>
+        <v>10100</v>
       </c>
       <c r="E57" s="3">
+        <v>17100</v>
+      </c>
+      <c r="F57" s="3">
         <v>3300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1000</v>
-      </c>
-      <c r="J57" s="3">
-        <v>1100</v>
       </c>
       <c r="K57" s="3">
         <v>1100</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
+      <c r="L57" s="3">
+        <v>1100</v>
       </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
@@ -2567,29 +2697,32 @@
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>33600</v>
+        <v>16200</v>
       </c>
       <c r="E58" s="3">
-        <v>56500</v>
+        <v>41200</v>
       </c>
       <c r="F58" s="3">
-        <v>20900</v>
+        <v>56100</v>
       </c>
       <c r="G58" s="3">
+        <v>20700</v>
+      </c>
+      <c r="H58" s="3">
         <v>8300</v>
       </c>
-      <c r="H58" s="3">
-        <v>16700</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
+      <c r="I58" s="3">
+        <v>16600</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>3</v>
@@ -2606,42 +2739,45 @@
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>135200</v>
+        <v>159100</v>
       </c>
       <c r="E59" s="3">
-        <v>114000</v>
+        <v>236500</v>
       </c>
       <c r="F59" s="3">
-        <v>97300</v>
+        <v>113300</v>
       </c>
       <c r="G59" s="3">
-        <v>100100</v>
+        <v>96700</v>
       </c>
       <c r="H59" s="3">
-        <v>179900</v>
+        <v>99400</v>
       </c>
       <c r="I59" s="3">
-        <v>91200</v>
+        <v>178800</v>
       </c>
       <c r="J59" s="3">
+        <v>90600</v>
+      </c>
+      <c r="K59" s="3">
         <v>67300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>51500</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2651,39 +2787,42 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>171700</v>
+        <v>185400</v>
       </c>
       <c r="E60" s="3">
-        <v>173800</v>
+        <v>213300</v>
       </c>
       <c r="F60" s="3">
-        <v>120900</v>
+        <v>172700</v>
       </c>
       <c r="G60" s="3">
-        <v>110500</v>
+        <v>120100</v>
       </c>
       <c r="H60" s="3">
-        <v>98700</v>
+        <v>109800</v>
       </c>
       <c r="I60" s="3">
-        <v>92200</v>
+        <v>98100</v>
       </c>
       <c r="J60" s="3">
+        <v>91600</v>
+      </c>
+      <c r="K60" s="3">
         <v>68300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>52500</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2693,20 +2832,23 @@
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>22200</v>
+        <v>7800</v>
       </c>
       <c r="E61" s="3">
-        <v>42000</v>
+        <v>22100</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>41700</v>
       </c>
       <c r="G61" s="3">
         <v>0</v>
@@ -2735,39 +2877,42 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>307600</v>
+        <v>302300</v>
       </c>
       <c r="E62" s="3">
-        <v>149100</v>
+        <v>320700</v>
       </c>
       <c r="F62" s="3">
-        <v>135600</v>
+        <v>148200</v>
       </c>
       <c r="G62" s="3">
-        <v>139500</v>
+        <v>134800</v>
       </c>
       <c r="H62" s="3">
-        <v>150600</v>
+        <v>138700</v>
       </c>
       <c r="I62" s="3">
-        <v>50100</v>
+        <v>149700</v>
       </c>
       <c r="J62" s="3">
+        <v>49800</v>
+      </c>
+      <c r="K62" s="3">
         <v>49700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>37900</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2777,9 +2922,12 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2819,9 +2967,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2861,9 +3012,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2903,39 +3057,42 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>507700</v>
+        <v>500800</v>
       </c>
       <c r="E66" s="3">
-        <v>390600</v>
+        <v>562600</v>
       </c>
       <c r="F66" s="3">
-        <v>276900</v>
+        <v>388100</v>
       </c>
       <c r="G66" s="3">
-        <v>271800</v>
+        <v>275200</v>
       </c>
       <c r="H66" s="3">
-        <v>198600</v>
+        <v>270100</v>
       </c>
       <c r="I66" s="3">
-        <v>142300</v>
+        <v>197400</v>
       </c>
       <c r="J66" s="3">
+        <v>141400</v>
+      </c>
+      <c r="K66" s="3">
         <v>118100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>90600</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2945,9 +3102,12 @@
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2964,8 +3124,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3005,9 +3166,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3047,9 +3211,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3089,9 +3256,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3131,39 +3301,42 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-7800</v>
+        <v>-78500</v>
       </c>
       <c r="E72" s="3">
-        <v>45400</v>
+        <v>-113000</v>
       </c>
       <c r="F72" s="3">
-        <v>79200</v>
+        <v>45100</v>
       </c>
       <c r="G72" s="3">
-        <v>42900</v>
+        <v>78800</v>
       </c>
       <c r="H72" s="3">
-        <v>35100</v>
+        <v>42600</v>
       </c>
       <c r="I72" s="3">
-        <v>31000</v>
+        <v>34900</v>
       </c>
       <c r="J72" s="3">
+        <v>30800</v>
+      </c>
+      <c r="K72" s="3">
         <v>77400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>44300</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3173,9 +3346,12 @@
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3215,9 +3391,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3257,9 +3436,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3299,39 +3481,42 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>200800</v>
+        <v>199300</v>
       </c>
       <c r="E76" s="3">
-        <v>258300</v>
+        <v>222700</v>
       </c>
       <c r="F76" s="3">
-        <v>292400</v>
+        <v>256700</v>
       </c>
       <c r="G76" s="3">
-        <v>258700</v>
+        <v>290600</v>
       </c>
       <c r="H76" s="3">
-        <v>229500</v>
+        <v>257100</v>
       </c>
       <c r="I76" s="3">
-        <v>101800</v>
+        <v>228100</v>
       </c>
       <c r="J76" s="3">
+        <v>101200</v>
+      </c>
+      <c r="K76" s="3">
         <v>142700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>111500</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3341,9 +3526,12 @@
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3383,44 +3571,47 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3430,39 +3621,42 @@
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-53100</v>
+        <v>37200</v>
       </c>
       <c r="E81" s="3">
-        <v>16300</v>
+        <v>-58700</v>
       </c>
       <c r="F81" s="3">
-        <v>36300</v>
+        <v>12300</v>
       </c>
       <c r="G81" s="3">
-        <v>61500</v>
+        <v>36100</v>
       </c>
       <c r="H81" s="3">
-        <v>51700</v>
+        <v>61200</v>
       </c>
       <c r="I81" s="3">
-        <v>38000</v>
+        <v>51400</v>
       </c>
       <c r="J81" s="3">
+        <v>37800</v>
+      </c>
+      <c r="K81" s="3">
         <v>37000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>33900</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3472,9 +3666,12 @@
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3491,38 +3688,39 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>15300</v>
+        <v>16100</v>
       </c>
       <c r="E83" s="3">
-        <v>13600</v>
+        <v>17300</v>
       </c>
       <c r="F83" s="3">
-        <v>9200</v>
+        <v>16500</v>
       </c>
       <c r="G83" s="3">
+        <v>9100</v>
+      </c>
+      <c r="H83" s="3">
         <v>5600</v>
-      </c>
-      <c r="H83" s="3">
-        <v>3600</v>
       </c>
       <c r="I83" s="3">
         <v>3500</v>
       </c>
       <c r="J83" s="3">
+        <v>3400</v>
+      </c>
+      <c r="K83" s="3">
         <v>4900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>6000</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3532,9 +3730,12 @@
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3574,9 +3775,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3616,9 +3820,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3658,9 +3865,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3700,9 +3910,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3742,39 +3955,42 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>40600</v>
+        <v>62900</v>
       </c>
       <c r="E89" s="3">
-        <v>50200</v>
+        <v>40700</v>
       </c>
       <c r="F89" s="3">
-        <v>41000</v>
+        <v>52400</v>
       </c>
       <c r="G89" s="3">
-        <v>71400</v>
+        <v>40800</v>
       </c>
       <c r="H89" s="3">
-        <v>77100</v>
+        <v>71000</v>
       </c>
       <c r="I89" s="3">
-        <v>65300</v>
+        <v>76700</v>
       </c>
       <c r="J89" s="3">
+        <v>64900</v>
+      </c>
+      <c r="K89" s="3">
         <v>61700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>51300</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3784,9 +4000,12 @@
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3803,38 +4022,39 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-9600</v>
+        <v>-12100</v>
       </c>
       <c r="E91" s="3">
-        <v>-78000</v>
+        <v>-11600</v>
       </c>
       <c r="F91" s="3">
-        <v>-15600</v>
+        <v>-80400</v>
       </c>
       <c r="G91" s="3">
-        <v>-29700</v>
+        <v>-15500</v>
       </c>
       <c r="H91" s="3">
-        <v>-19300</v>
+        <v>-29500</v>
       </c>
       <c r="I91" s="3">
+        <v>-19100</v>
+      </c>
+      <c r="J91" s="3">
         <v>-2300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1900</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M91" s="3" t="s">
         <v>3</v>
       </c>
@@ -3844,9 +4064,12 @@
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3886,9 +4109,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3928,39 +4154,42 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>55400</v>
+        <v>-12900</v>
       </c>
       <c r="E94" s="3">
-        <v>-129100</v>
+        <v>58100</v>
       </c>
       <c r="F94" s="3">
-        <v>-15500</v>
+        <v>-135100</v>
       </c>
       <c r="G94" s="3">
-        <v>-169600</v>
+        <v>-15400</v>
       </c>
       <c r="H94" s="3">
-        <v>-25300</v>
+        <v>-168500</v>
       </c>
       <c r="I94" s="3">
-        <v>-103500</v>
+        <v>-25100</v>
       </c>
       <c r="J94" s="3">
+        <v>-102900</v>
+      </c>
+      <c r="K94" s="3">
         <v>10300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-26800</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3970,9 +4199,12 @@
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3989,28 +4221,29 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
         <v>-5700</v>
       </c>
-      <c r="E96" s="3">
-        <v>-44500</v>
-      </c>
       <c r="F96" s="3">
-        <v>0</v>
+        <v>-44200</v>
       </c>
       <c r="G96" s="3">
-        <v>-31600</v>
+        <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>-27900</v>
+        <v>-31400</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
+        <v>-27700</v>
       </c>
       <c r="J96" s="3">
         <v>0</v>
@@ -4030,9 +4263,12 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4072,9 +4308,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4114,9 +4353,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4156,39 +4398,42 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-47500</v>
+        <v>-42000</v>
       </c>
       <c r="E100" s="3">
-        <v>35500</v>
+        <v>-46300</v>
       </c>
       <c r="F100" s="3">
-        <v>16100</v>
+        <v>33200</v>
       </c>
       <c r="G100" s="3">
-        <v>-29500</v>
+        <v>16000</v>
       </c>
       <c r="H100" s="3">
-        <v>92200</v>
+        <v>-29300</v>
       </c>
       <c r="I100" s="3">
-        <v>-89700</v>
+        <v>91600</v>
       </c>
       <c r="J100" s="3">
+        <v>-89100</v>
+      </c>
+      <c r="K100" s="3">
         <v>-18500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-7400</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4198,39 +4443,42 @@
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E101" s="3">
+        <v>200</v>
+      </c>
+      <c r="F101" s="3">
         <v>-200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1000</v>
       </c>
-      <c r="H101" s="3">
-        <v>9200</v>
-      </c>
       <c r="I101" s="3">
+        <v>9100</v>
+      </c>
+      <c r="J101" s="3">
         <v>-200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>800</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
@@ -4240,39 +4488,42 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>48600</v>
+        <v>8000</v>
       </c>
       <c r="E102" s="3">
-        <v>-43500</v>
+        <v>52600</v>
       </c>
       <c r="F102" s="3">
-        <v>40500</v>
+        <v>-49700</v>
       </c>
       <c r="G102" s="3">
-        <v>-128600</v>
+        <v>40300</v>
       </c>
       <c r="H102" s="3">
-        <v>153300</v>
+        <v>-127800</v>
       </c>
       <c r="I102" s="3">
-        <v>-128200</v>
+        <v>152300</v>
       </c>
       <c r="J102" s="3">
+        <v>-127400</v>
+      </c>
+      <c r="K102" s="3">
         <v>54300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>17900</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4282,7 +4533,10 @@
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/GHG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/GHG_YR_FIN.xlsx
@@ -727,25 +727,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>224800</v>
+        <v>229400</v>
       </c>
       <c r="E8" s="3">
-        <v>203000</v>
+        <v>207100</v>
       </c>
       <c r="F8" s="3">
-        <v>271900</v>
+        <v>277400</v>
       </c>
       <c r="G8" s="3">
-        <v>128500</v>
+        <v>131100</v>
       </c>
       <c r="H8" s="3">
-        <v>150800</v>
+        <v>153900</v>
       </c>
       <c r="I8" s="3">
-        <v>125100</v>
+        <v>127700</v>
       </c>
       <c r="J8" s="3">
-        <v>102700</v>
+        <v>104800</v>
       </c>
       <c r="K8" s="3">
         <v>90100</v>
@@ -790,7 +790,7 @@
         <v>3</v>
       </c>
       <c r="J9" s="3">
-        <v>7000</v>
+        <v>7100</v>
       </c>
       <c r="K9" s="3">
         <v>9200</v>
@@ -835,7 +835,7 @@
         <v>3</v>
       </c>
       <c r="J10" s="3">
-        <v>95700</v>
+        <v>97600</v>
       </c>
       <c r="K10" s="3">
         <v>80800</v>
@@ -974,7 +974,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="3">
-        <v>24000</v>
+        <v>24500</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
@@ -1016,22 +1016,22 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>12800</v>
+        <v>13100</v>
       </c>
       <c r="E15" s="3">
-        <v>14400</v>
+        <v>14700</v>
       </c>
       <c r="F15" s="3">
-        <v>14900</v>
+        <v>15200</v>
       </c>
       <c r="G15" s="3">
-        <v>8300</v>
+        <v>8400</v>
       </c>
       <c r="H15" s="3">
-        <v>5200</v>
+        <v>5300</v>
       </c>
       <c r="I15" s="3">
-        <v>3300</v>
+        <v>3400</v>
       </c>
       <c r="J15" s="3">
         <v>200</v>
@@ -1077,25 +1077,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>178400</v>
+        <v>182100</v>
       </c>
       <c r="E17" s="3">
-        <v>276000</v>
+        <v>281600</v>
       </c>
       <c r="F17" s="3">
-        <v>254000</v>
+        <v>259200</v>
       </c>
       <c r="G17" s="3">
-        <v>84400</v>
+        <v>86100</v>
       </c>
       <c r="H17" s="3">
-        <v>81100</v>
+        <v>82800</v>
       </c>
       <c r="I17" s="3">
-        <v>55300</v>
+        <v>56500</v>
       </c>
       <c r="J17" s="3">
-        <v>51400</v>
+        <v>52400</v>
       </c>
       <c r="K17" s="3">
         <v>46600</v>
@@ -1122,25 +1122,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>46400</v>
+        <v>47300</v>
       </c>
       <c r="E18" s="3">
-        <v>-73000</v>
+        <v>-74500</v>
       </c>
       <c r="F18" s="3">
-        <v>17900</v>
+        <v>18200</v>
       </c>
       <c r="G18" s="3">
-        <v>44100</v>
+        <v>45000</v>
       </c>
       <c r="H18" s="3">
-        <v>69700</v>
+        <v>71100</v>
       </c>
       <c r="I18" s="3">
-        <v>69800</v>
+        <v>71200</v>
       </c>
       <c r="J18" s="3">
-        <v>51300</v>
+        <v>52400</v>
       </c>
       <c r="K18" s="3">
         <v>43400</v>
@@ -1186,25 +1186,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>8100</v>
+        <v>8300</v>
       </c>
       <c r="E20" s="3">
-        <v>7200</v>
+        <v>7400</v>
       </c>
       <c r="F20" s="3">
-        <v>11300</v>
+        <v>11500</v>
       </c>
       <c r="G20" s="3">
-        <v>5300</v>
+        <v>5400</v>
       </c>
       <c r="H20" s="3">
-        <v>17100</v>
+        <v>17500</v>
       </c>
       <c r="I20" s="3">
-        <v>3800</v>
+        <v>3900</v>
       </c>
       <c r="J20" s="3">
-        <v>12000</v>
+        <v>12200</v>
       </c>
       <c r="K20" s="3">
         <v>6700</v>
@@ -1231,25 +1231,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>70600</v>
+        <v>72000</v>
       </c>
       <c r="E21" s="3">
-        <v>-48500</v>
+        <v>-49500</v>
       </c>
       <c r="F21" s="3">
-        <v>45600</v>
+        <v>46500</v>
       </c>
       <c r="G21" s="3">
-        <v>58500</v>
+        <v>59700</v>
       </c>
       <c r="H21" s="3">
-        <v>92400</v>
+        <v>94300</v>
       </c>
       <c r="I21" s="3">
-        <v>77100</v>
+        <v>78700</v>
       </c>
       <c r="J21" s="3">
-        <v>66700</v>
+        <v>68100</v>
       </c>
       <c r="K21" s="3">
         <v>55000</v>
@@ -1276,19 +1276,19 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>1900</v>
+        <v>2000</v>
       </c>
       <c r="E22" s="3">
         <v>3900</v>
       </c>
       <c r="F22" s="3">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="G22" s="3">
         <v>500</v>
       </c>
       <c r="H22" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="I22" s="3">
         <v>100</v>
@@ -1321,25 +1321,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>52600</v>
+        <v>53600</v>
       </c>
       <c r="E23" s="3">
-        <v>-69700</v>
+        <v>-71100</v>
       </c>
       <c r="F23" s="3">
-        <v>27000</v>
+        <v>27600</v>
       </c>
       <c r="G23" s="3">
-        <v>48900</v>
+        <v>49900</v>
       </c>
       <c r="H23" s="3">
-        <v>86500</v>
+        <v>88300</v>
       </c>
       <c r="I23" s="3">
-        <v>73500</v>
+        <v>75000</v>
       </c>
       <c r="J23" s="3">
-        <v>63100</v>
+        <v>64400</v>
       </c>
       <c r="K23" s="3">
         <v>50100</v>
@@ -1366,25 +1366,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>16400</v>
+        <v>16700</v>
       </c>
       <c r="E24" s="3">
-        <v>-6100</v>
+        <v>-6200</v>
       </c>
       <c r="F24" s="3">
-        <v>15500</v>
+        <v>15800</v>
       </c>
       <c r="G24" s="3">
-        <v>15300</v>
+        <v>15600</v>
       </c>
       <c r="H24" s="3">
-        <v>26200</v>
+        <v>26700</v>
       </c>
       <c r="I24" s="3">
-        <v>21100</v>
+        <v>21500</v>
       </c>
       <c r="J24" s="3">
-        <v>25200</v>
+        <v>25700</v>
       </c>
       <c r="K24" s="3">
         <v>11700</v>
@@ -1456,25 +1456,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>36200</v>
+        <v>36900</v>
       </c>
       <c r="E26" s="3">
-        <v>-63600</v>
+        <v>-64900</v>
       </c>
       <c r="F26" s="3">
-        <v>11500</v>
+        <v>11700</v>
       </c>
       <c r="G26" s="3">
-        <v>33700</v>
+        <v>34400</v>
       </c>
       <c r="H26" s="3">
-        <v>60300</v>
+        <v>61500</v>
       </c>
       <c r="I26" s="3">
-        <v>52400</v>
+        <v>53500</v>
       </c>
       <c r="J26" s="3">
-        <v>37900</v>
+        <v>38600</v>
       </c>
       <c r="K26" s="3">
         <v>38400</v>
@@ -1501,25 +1501,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>37200</v>
+        <v>38000</v>
       </c>
       <c r="E27" s="3">
-        <v>-58700</v>
+        <v>-59900</v>
       </c>
       <c r="F27" s="3">
-        <v>12300</v>
+        <v>12500</v>
       </c>
       <c r="G27" s="3">
-        <v>36100</v>
+        <v>36800</v>
       </c>
       <c r="H27" s="3">
-        <v>61200</v>
+        <v>62400</v>
       </c>
       <c r="I27" s="3">
-        <v>51400</v>
+        <v>52400</v>
       </c>
       <c r="J27" s="3">
-        <v>37800</v>
+        <v>38600</v>
       </c>
       <c r="K27" s="3">
         <v>37000</v>
@@ -1726,25 +1726,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-8100</v>
+        <v>-8300</v>
       </c>
       <c r="E32" s="3">
-        <v>-7200</v>
+        <v>-7400</v>
       </c>
       <c r="F32" s="3">
-        <v>-11300</v>
+        <v>-11500</v>
       </c>
       <c r="G32" s="3">
-        <v>-5300</v>
+        <v>-5400</v>
       </c>
       <c r="H32" s="3">
-        <v>-17100</v>
+        <v>-17500</v>
       </c>
       <c r="I32" s="3">
-        <v>-3800</v>
+        <v>-3900</v>
       </c>
       <c r="J32" s="3">
-        <v>-12000</v>
+        <v>-12200</v>
       </c>
       <c r="K32" s="3">
         <v>-6700</v>
@@ -1771,25 +1771,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>37200</v>
+        <v>38000</v>
       </c>
       <c r="E33" s="3">
-        <v>-58700</v>
+        <v>-59900</v>
       </c>
       <c r="F33" s="3">
-        <v>12300</v>
+        <v>12500</v>
       </c>
       <c r="G33" s="3">
-        <v>36100</v>
+        <v>36800</v>
       </c>
       <c r="H33" s="3">
-        <v>61200</v>
+        <v>62400</v>
       </c>
       <c r="I33" s="3">
-        <v>51400</v>
+        <v>52400</v>
       </c>
       <c r="J33" s="3">
-        <v>37800</v>
+        <v>38600</v>
       </c>
       <c r="K33" s="3">
         <v>37000</v>
@@ -1861,25 +1861,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>37200</v>
+        <v>38000</v>
       </c>
       <c r="E35" s="3">
-        <v>-58700</v>
+        <v>-59900</v>
       </c>
       <c r="F35" s="3">
-        <v>12300</v>
+        <v>12500</v>
       </c>
       <c r="G35" s="3">
-        <v>36100</v>
+        <v>36800</v>
       </c>
       <c r="H35" s="3">
-        <v>61200</v>
+        <v>62400</v>
       </c>
       <c r="I35" s="3">
-        <v>51400</v>
+        <v>52400</v>
       </c>
       <c r="J35" s="3">
-        <v>37800</v>
+        <v>38600</v>
       </c>
       <c r="K35" s="3">
         <v>37000</v>
@@ -1994,25 +1994,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>105800</v>
+        <v>107900</v>
       </c>
       <c r="E41" s="3">
-        <v>96600</v>
+        <v>98600</v>
       </c>
       <c r="F41" s="3">
-        <v>41200</v>
+        <v>42100</v>
       </c>
       <c r="G41" s="3">
-        <v>84500</v>
+        <v>86200</v>
       </c>
       <c r="H41" s="3">
-        <v>44200</v>
+        <v>45100</v>
       </c>
       <c r="I41" s="3">
-        <v>174600</v>
+        <v>178200</v>
       </c>
       <c r="J41" s="3">
-        <v>22400</v>
+        <v>22800</v>
       </c>
       <c r="K41" s="3">
         <v>124700</v>
@@ -2039,25 +2039,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>61300</v>
+        <v>62600</v>
       </c>
       <c r="E42" s="3">
-        <v>31400</v>
+        <v>32100</v>
       </c>
       <c r="F42" s="3">
-        <v>98800</v>
+        <v>100900</v>
       </c>
       <c r="G42" s="3">
-        <v>75200</v>
+        <v>76700</v>
       </c>
       <c r="H42" s="3">
-        <v>89000</v>
+        <v>90800</v>
       </c>
       <c r="I42" s="3">
-        <v>137200</v>
+        <v>140000</v>
       </c>
       <c r="J42" s="3">
-        <v>150500</v>
+        <v>153600</v>
       </c>
       <c r="K42" s="3">
         <v>38000</v>
@@ -2084,25 +2084,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>39700</v>
+        <v>40500</v>
       </c>
       <c r="E43" s="3">
-        <v>103200</v>
+        <v>105400</v>
       </c>
       <c r="F43" s="3">
-        <v>97100</v>
+        <v>99100</v>
       </c>
       <c r="G43" s="3">
-        <v>46100</v>
+        <v>47000</v>
       </c>
       <c r="H43" s="3">
-        <v>29500</v>
+        <v>30100</v>
       </c>
       <c r="I43" s="3">
-        <v>27200</v>
+        <v>27800</v>
       </c>
       <c r="J43" s="3">
-        <v>8800</v>
+        <v>9000</v>
       </c>
       <c r="K43" s="3">
         <v>25800</v>
@@ -2129,10 +2129,10 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>2800</v>
+        <v>2900</v>
       </c>
       <c r="E44" s="3">
-        <v>3000</v>
+        <v>3100</v>
       </c>
       <c r="F44" s="3">
         <v>300</v>
@@ -2174,25 +2174,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>15200</v>
+        <v>15500</v>
       </c>
       <c r="E45" s="3">
-        <v>16400</v>
+        <v>16700</v>
       </c>
       <c r="F45" s="3">
-        <v>15500</v>
+        <v>15800</v>
       </c>
       <c r="G45" s="3">
-        <v>12600</v>
+        <v>12900</v>
       </c>
       <c r="H45" s="3">
-        <v>11700</v>
+        <v>12000</v>
       </c>
       <c r="I45" s="3">
-        <v>8100</v>
+        <v>8200</v>
       </c>
       <c r="J45" s="3">
-        <v>23200</v>
+        <v>23700</v>
       </c>
       <c r="K45" s="3">
         <v>33800</v>
@@ -2219,25 +2219,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>224800</v>
+        <v>229300</v>
       </c>
       <c r="E46" s="3">
-        <v>250700</v>
+        <v>255800</v>
       </c>
       <c r="F46" s="3">
-        <v>253000</v>
+        <v>258200</v>
       </c>
       <c r="G46" s="3">
-        <v>218900</v>
+        <v>223400</v>
       </c>
       <c r="H46" s="3">
-        <v>174800</v>
+        <v>178400</v>
       </c>
       <c r="I46" s="3">
-        <v>338600</v>
+        <v>345500</v>
       </c>
       <c r="J46" s="3">
-        <v>205200</v>
+        <v>209400</v>
       </c>
       <c r="K46" s="3">
         <v>222600</v>
@@ -2264,25 +2264,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>61100</v>
+        <v>62400</v>
       </c>
       <c r="E47" s="3">
-        <v>83100</v>
+        <v>84800</v>
       </c>
       <c r="F47" s="3">
-        <v>89200</v>
+        <v>91000</v>
       </c>
       <c r="G47" s="3">
-        <v>143500</v>
+        <v>146500</v>
       </c>
       <c r="H47" s="3">
-        <v>149200</v>
+        <v>152300</v>
       </c>
       <c r="I47" s="3">
-        <v>59100</v>
+        <v>60300</v>
       </c>
       <c r="J47" s="3">
-        <v>17300</v>
+        <v>17600</v>
       </c>
       <c r="K47" s="3">
         <v>4900</v>
@@ -2309,25 +2309,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>324700</v>
+        <v>331300</v>
       </c>
       <c r="E48" s="3">
-        <v>353400</v>
+        <v>360600</v>
       </c>
       <c r="F48" s="3">
-        <v>144400</v>
+        <v>147400</v>
       </c>
       <c r="G48" s="3">
-        <v>92400</v>
+        <v>94300</v>
       </c>
       <c r="H48" s="3">
-        <v>85000</v>
+        <v>86700</v>
       </c>
       <c r="I48" s="3">
-        <v>61500</v>
+        <v>62700</v>
       </c>
       <c r="J48" s="3">
-        <v>13400</v>
+        <v>13600</v>
       </c>
       <c r="K48" s="3">
         <v>15400</v>
@@ -2354,22 +2354,22 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>40700</v>
+        <v>41600</v>
       </c>
       <c r="E49" s="3">
-        <v>43200</v>
+        <v>44100</v>
       </c>
       <c r="F49" s="3">
-        <v>88600</v>
+        <v>90400</v>
       </c>
       <c r="G49" s="3">
-        <v>81800</v>
+        <v>83400</v>
       </c>
       <c r="H49" s="3">
-        <v>82400</v>
+        <v>84100</v>
       </c>
       <c r="I49" s="3">
-        <v>8300</v>
+        <v>8500</v>
       </c>
       <c r="J49" s="3">
         <v>900</v>
@@ -2489,25 +2489,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>48700</v>
+        <v>49700</v>
       </c>
       <c r="E52" s="3">
-        <v>51600</v>
+        <v>52700</v>
       </c>
       <c r="F52" s="3">
-        <v>69600</v>
+        <v>71100</v>
       </c>
       <c r="G52" s="3">
-        <v>29200</v>
+        <v>29800</v>
       </c>
       <c r="H52" s="3">
-        <v>35900</v>
+        <v>36600</v>
       </c>
       <c r="I52" s="3">
-        <v>22400</v>
+        <v>22900</v>
       </c>
       <c r="J52" s="3">
-        <v>5800</v>
+        <v>5900</v>
       </c>
       <c r="K52" s="3">
         <v>16800</v>
@@ -2579,25 +2579,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>700000</v>
+        <v>714300</v>
       </c>
       <c r="E54" s="3">
-        <v>785300</v>
+        <v>801300</v>
       </c>
       <c r="F54" s="3">
-        <v>644800</v>
+        <v>658000</v>
       </c>
       <c r="G54" s="3">
-        <v>565800</v>
+        <v>577300</v>
       </c>
       <c r="H54" s="3">
-        <v>527300</v>
+        <v>538000</v>
       </c>
       <c r="I54" s="3">
-        <v>425500</v>
+        <v>434200</v>
       </c>
       <c r="J54" s="3">
-        <v>242600</v>
+        <v>247600</v>
       </c>
       <c r="K54" s="3">
         <v>260800</v>
@@ -2662,19 +2662,19 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>10100</v>
+        <v>10300</v>
       </c>
       <c r="E57" s="3">
-        <v>17100</v>
+        <v>17400</v>
       </c>
       <c r="F57" s="3">
-        <v>3300</v>
+        <v>3400</v>
       </c>
       <c r="G57" s="3">
-        <v>2700</v>
+        <v>2800</v>
       </c>
       <c r="H57" s="3">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="I57" s="3">
         <v>1300</v>
@@ -2707,22 +2707,22 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>16200</v>
+        <v>16500</v>
       </c>
       <c r="E58" s="3">
-        <v>41200</v>
+        <v>42000</v>
       </c>
       <c r="F58" s="3">
-        <v>56100</v>
+        <v>57300</v>
       </c>
       <c r="G58" s="3">
-        <v>20700</v>
+        <v>21100</v>
       </c>
       <c r="H58" s="3">
-        <v>8300</v>
+        <v>8500</v>
       </c>
       <c r="I58" s="3">
-        <v>16600</v>
+        <v>16900</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>3</v>
@@ -2752,25 +2752,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>159100</v>
+        <v>162300</v>
       </c>
       <c r="E59" s="3">
-        <v>236500</v>
+        <v>241300</v>
       </c>
       <c r="F59" s="3">
-        <v>113300</v>
+        <v>115600</v>
       </c>
       <c r="G59" s="3">
-        <v>96700</v>
+        <v>98700</v>
       </c>
       <c r="H59" s="3">
-        <v>99400</v>
+        <v>101500</v>
       </c>
       <c r="I59" s="3">
-        <v>178800</v>
+        <v>182400</v>
       </c>
       <c r="J59" s="3">
-        <v>90600</v>
+        <v>92400</v>
       </c>
       <c r="K59" s="3">
         <v>67300</v>
@@ -2797,25 +2797,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>185400</v>
+        <v>189100</v>
       </c>
       <c r="E60" s="3">
-        <v>213300</v>
+        <v>217700</v>
       </c>
       <c r="F60" s="3">
-        <v>172700</v>
+        <v>176200</v>
       </c>
       <c r="G60" s="3">
-        <v>120100</v>
+        <v>122600</v>
       </c>
       <c r="H60" s="3">
-        <v>109800</v>
+        <v>112100</v>
       </c>
       <c r="I60" s="3">
-        <v>98100</v>
+        <v>100100</v>
       </c>
       <c r="J60" s="3">
-        <v>91600</v>
+        <v>93500</v>
       </c>
       <c r="K60" s="3">
         <v>68300</v>
@@ -2842,13 +2842,13 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>7800</v>
+        <v>8000</v>
       </c>
       <c r="E61" s="3">
-        <v>22100</v>
+        <v>22600</v>
       </c>
       <c r="F61" s="3">
-        <v>41700</v>
+        <v>42500</v>
       </c>
       <c r="G61" s="3">
         <v>0</v>
@@ -2887,25 +2887,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>302300</v>
+        <v>308500</v>
       </c>
       <c r="E62" s="3">
-        <v>320700</v>
+        <v>327300</v>
       </c>
       <c r="F62" s="3">
-        <v>148200</v>
+        <v>151200</v>
       </c>
       <c r="G62" s="3">
-        <v>134800</v>
+        <v>137500</v>
       </c>
       <c r="H62" s="3">
-        <v>138700</v>
+        <v>141500</v>
       </c>
       <c r="I62" s="3">
-        <v>149700</v>
+        <v>152800</v>
       </c>
       <c r="J62" s="3">
-        <v>49800</v>
+        <v>50800</v>
       </c>
       <c r="K62" s="3">
         <v>49700</v>
@@ -3067,25 +3067,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>500800</v>
+        <v>511000</v>
       </c>
       <c r="E66" s="3">
-        <v>562600</v>
+        <v>574100</v>
       </c>
       <c r="F66" s="3">
-        <v>388100</v>
+        <v>396100</v>
       </c>
       <c r="G66" s="3">
-        <v>275200</v>
+        <v>280800</v>
       </c>
       <c r="H66" s="3">
-        <v>270100</v>
+        <v>275700</v>
       </c>
       <c r="I66" s="3">
-        <v>197400</v>
+        <v>201400</v>
       </c>
       <c r="J66" s="3">
-        <v>141400</v>
+        <v>144300</v>
       </c>
       <c r="K66" s="3">
         <v>118100</v>
@@ -3311,25 +3311,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-78500</v>
+        <v>-80100</v>
       </c>
       <c r="E72" s="3">
-        <v>-113000</v>
+        <v>-115300</v>
       </c>
       <c r="F72" s="3">
-        <v>45100</v>
+        <v>46000</v>
       </c>
       <c r="G72" s="3">
-        <v>78800</v>
+        <v>80400</v>
       </c>
       <c r="H72" s="3">
-        <v>42600</v>
+        <v>43500</v>
       </c>
       <c r="I72" s="3">
-        <v>34900</v>
+        <v>35600</v>
       </c>
       <c r="J72" s="3">
-        <v>30800</v>
+        <v>31500</v>
       </c>
       <c r="K72" s="3">
         <v>77400</v>
@@ -3491,25 +3491,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>199300</v>
+        <v>203300</v>
       </c>
       <c r="E76" s="3">
-        <v>222700</v>
+        <v>227200</v>
       </c>
       <c r="F76" s="3">
-        <v>256700</v>
+        <v>261900</v>
       </c>
       <c r="G76" s="3">
-        <v>290600</v>
+        <v>296500</v>
       </c>
       <c r="H76" s="3">
-        <v>257100</v>
+        <v>262400</v>
       </c>
       <c r="I76" s="3">
-        <v>228100</v>
+        <v>232800</v>
       </c>
       <c r="J76" s="3">
-        <v>101200</v>
+        <v>103200</v>
       </c>
       <c r="K76" s="3">
         <v>142700</v>
@@ -3631,25 +3631,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>37200</v>
+        <v>38000</v>
       </c>
       <c r="E81" s="3">
-        <v>-58700</v>
+        <v>-59900</v>
       </c>
       <c r="F81" s="3">
-        <v>12300</v>
+        <v>12500</v>
       </c>
       <c r="G81" s="3">
-        <v>36100</v>
+        <v>36800</v>
       </c>
       <c r="H81" s="3">
-        <v>61200</v>
+        <v>62400</v>
       </c>
       <c r="I81" s="3">
-        <v>51400</v>
+        <v>52400</v>
       </c>
       <c r="J81" s="3">
-        <v>37800</v>
+        <v>38600</v>
       </c>
       <c r="K81" s="3">
         <v>37000</v>
@@ -3695,25 +3695,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>16100</v>
+        <v>16500</v>
       </c>
       <c r="E83" s="3">
-        <v>17300</v>
+        <v>17700</v>
       </c>
       <c r="F83" s="3">
-        <v>16500</v>
+        <v>16800</v>
       </c>
       <c r="G83" s="3">
-        <v>9100</v>
+        <v>9300</v>
       </c>
       <c r="H83" s="3">
-        <v>5600</v>
+        <v>5700</v>
       </c>
       <c r="I83" s="3">
+        <v>3600</v>
+      </c>
+      <c r="J83" s="3">
         <v>3500</v>
-      </c>
-      <c r="J83" s="3">
-        <v>3400</v>
       </c>
       <c r="K83" s="3">
         <v>4900</v>
@@ -3965,25 +3965,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>62900</v>
+        <v>64200</v>
       </c>
       <c r="E89" s="3">
-        <v>40700</v>
+        <v>41500</v>
       </c>
       <c r="F89" s="3">
-        <v>52400</v>
+        <v>53500</v>
       </c>
       <c r="G89" s="3">
-        <v>40800</v>
+        <v>41600</v>
       </c>
       <c r="H89" s="3">
-        <v>71000</v>
+        <v>72500</v>
       </c>
       <c r="I89" s="3">
-        <v>76700</v>
+        <v>78200</v>
       </c>
       <c r="J89" s="3">
-        <v>64900</v>
+        <v>66200</v>
       </c>
       <c r="K89" s="3">
         <v>61700</v>
@@ -4029,22 +4029,22 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-12100</v>
+        <v>-12400</v>
       </c>
       <c r="E91" s="3">
-        <v>-11600</v>
+        <v>-11800</v>
       </c>
       <c r="F91" s="3">
-        <v>-80400</v>
+        <v>-82000</v>
       </c>
       <c r="G91" s="3">
-        <v>-15500</v>
+        <v>-15800</v>
       </c>
       <c r="H91" s="3">
-        <v>-29500</v>
+        <v>-30100</v>
       </c>
       <c r="I91" s="3">
-        <v>-19100</v>
+        <v>-19500</v>
       </c>
       <c r="J91" s="3">
         <v>-2300</v>
@@ -4164,25 +4164,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-12900</v>
+        <v>-13200</v>
       </c>
       <c r="E94" s="3">
-        <v>58100</v>
+        <v>59300</v>
       </c>
       <c r="F94" s="3">
-        <v>-135100</v>
+        <v>-137900</v>
       </c>
       <c r="G94" s="3">
-        <v>-15400</v>
+        <v>-15700</v>
       </c>
       <c r="H94" s="3">
-        <v>-168500</v>
+        <v>-172000</v>
       </c>
       <c r="I94" s="3">
-        <v>-25100</v>
+        <v>-25600</v>
       </c>
       <c r="J94" s="3">
-        <v>-102900</v>
+        <v>-105000</v>
       </c>
       <c r="K94" s="3">
         <v>10300</v>
@@ -4231,19 +4231,19 @@
         <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>-5700</v>
+        <v>-5800</v>
       </c>
       <c r="F96" s="3">
-        <v>-44200</v>
+        <v>-45100</v>
       </c>
       <c r="G96" s="3">
         <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>-31400</v>
+        <v>-32000</v>
       </c>
       <c r="I96" s="3">
-        <v>-27700</v>
+        <v>-28300</v>
       </c>
       <c r="J96" s="3">
         <v>0</v>
@@ -4408,25 +4408,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-42000</v>
+        <v>-42800</v>
       </c>
       <c r="E100" s="3">
-        <v>-46300</v>
+        <v>-47300</v>
       </c>
       <c r="F100" s="3">
-        <v>33200</v>
+        <v>33900</v>
       </c>
       <c r="G100" s="3">
-        <v>16000</v>
+        <v>16300</v>
       </c>
       <c r="H100" s="3">
-        <v>-29300</v>
+        <v>-29900</v>
       </c>
       <c r="I100" s="3">
-        <v>91600</v>
+        <v>93500</v>
       </c>
       <c r="J100" s="3">
-        <v>-89100</v>
+        <v>-91000</v>
       </c>
       <c r="K100" s="3">
         <v>-18500</v>
@@ -4468,7 +4468,7 @@
         <v>-1000</v>
       </c>
       <c r="I101" s="3">
-        <v>9100</v>
+        <v>9300</v>
       </c>
       <c r="J101" s="3">
         <v>-200</v>
@@ -4498,25 +4498,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>8000</v>
+        <v>8100</v>
       </c>
       <c r="E102" s="3">
-        <v>52600</v>
+        <v>53700</v>
       </c>
       <c r="F102" s="3">
-        <v>-49700</v>
+        <v>-50700</v>
       </c>
       <c r="G102" s="3">
-        <v>40300</v>
+        <v>41100</v>
       </c>
       <c r="H102" s="3">
-        <v>-127800</v>
+        <v>-130400</v>
       </c>
       <c r="I102" s="3">
-        <v>152300</v>
+        <v>155400</v>
       </c>
       <c r="J102" s="3">
-        <v>-127400</v>
+        <v>-130000</v>
       </c>
       <c r="K102" s="3">
         <v>54300</v>

--- a/AAII_Financials/Yearly/GHG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/GHG_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="92">
   <si>
     <t>GHG</t>
   </si>
@@ -727,25 +727,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>229400</v>
+        <v>229500</v>
       </c>
       <c r="E8" s="3">
-        <v>207100</v>
+        <v>213000</v>
       </c>
       <c r="F8" s="3">
-        <v>277400</v>
+        <v>309800</v>
       </c>
       <c r="G8" s="3">
-        <v>131100</v>
+        <v>142500</v>
       </c>
       <c r="H8" s="3">
-        <v>153900</v>
+        <v>156800</v>
       </c>
       <c r="I8" s="3">
-        <v>127700</v>
+        <v>131700</v>
       </c>
       <c r="J8" s="3">
-        <v>104800</v>
+        <v>114200</v>
       </c>
       <c r="K8" s="3">
         <v>90100</v>
@@ -771,26 +771,26 @@
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
+      <c r="D9" s="3">
+        <v>133600</v>
+      </c>
+      <c r="E9" s="3">
+        <v>154600</v>
+      </c>
+      <c r="F9" s="3">
+        <v>206600</v>
+      </c>
+      <c r="G9" s="3">
+        <v>61500</v>
+      </c>
+      <c r="H9" s="3">
+        <v>48700</v>
+      </c>
+      <c r="I9" s="3">
+        <v>39900</v>
       </c>
       <c r="J9" s="3">
-        <v>7100</v>
+        <v>34900</v>
       </c>
       <c r="K9" s="3">
         <v>9200</v>
@@ -816,26 +816,26 @@
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3">
+        <v>95900</v>
+      </c>
+      <c r="E10" s="3">
+        <v>58400</v>
+      </c>
+      <c r="F10" s="3">
+        <v>103200</v>
+      </c>
+      <c r="G10" s="3">
+        <v>80900</v>
+      </c>
+      <c r="H10" s="3">
+        <v>108100</v>
+      </c>
+      <c r="I10" s="3">
+        <v>91800</v>
       </c>
       <c r="J10" s="3">
-        <v>97600</v>
+        <v>79400</v>
       </c>
       <c r="K10" s="3">
         <v>80800</v>
@@ -971,25 +971,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>3300</v>
       </c>
       <c r="E14" s="3">
-        <v>24500</v>
+        <v>27400</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
+        <v>1300</v>
+      </c>
+      <c r="G14" s="3">
+        <v>5600</v>
+      </c>
+      <c r="H14" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="I14" s="3">
+        <v>8900</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>-3200</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1016,25 +1016,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>13100</v>
+        <v>16500</v>
       </c>
       <c r="E15" s="3">
-        <v>14700</v>
+        <v>18200</v>
       </c>
       <c r="F15" s="3">
-        <v>15200</v>
+        <v>18800</v>
       </c>
       <c r="G15" s="3">
-        <v>8400</v>
+        <v>10100</v>
       </c>
       <c r="H15" s="3">
-        <v>5300</v>
+        <v>5800</v>
       </c>
       <c r="I15" s="3">
-        <v>3400</v>
+        <v>3700</v>
       </c>
       <c r="J15" s="3">
-        <v>200</v>
+        <v>3800</v>
       </c>
       <c r="K15" s="3">
         <v>100</v>
@@ -1077,25 +1077,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>182100</v>
+        <v>179600</v>
       </c>
       <c r="E17" s="3">
-        <v>281600</v>
+        <v>265200</v>
       </c>
       <c r="F17" s="3">
-        <v>259200</v>
+        <v>286700</v>
       </c>
       <c r="G17" s="3">
-        <v>86100</v>
+        <v>93600</v>
       </c>
       <c r="H17" s="3">
-        <v>82800</v>
+        <v>83800</v>
       </c>
       <c r="I17" s="3">
-        <v>56500</v>
+        <v>57500</v>
       </c>
       <c r="J17" s="3">
-        <v>52400</v>
+        <v>51300</v>
       </c>
       <c r="K17" s="3">
         <v>46600</v>
@@ -1122,25 +1122,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>47300</v>
+        <v>49900</v>
       </c>
       <c r="E18" s="3">
-        <v>-74500</v>
+        <v>-52200</v>
       </c>
       <c r="F18" s="3">
-        <v>18200</v>
+        <v>23100</v>
       </c>
       <c r="G18" s="3">
-        <v>45000</v>
+        <v>48900</v>
       </c>
       <c r="H18" s="3">
-        <v>71100</v>
+        <v>73000</v>
       </c>
       <c r="I18" s="3">
-        <v>71200</v>
+        <v>74200</v>
       </c>
       <c r="J18" s="3">
-        <v>52400</v>
+        <v>62900</v>
       </c>
       <c r="K18" s="3">
         <v>43400</v>
@@ -1186,25 +1186,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>8300</v>
+        <v>-3000</v>
       </c>
       <c r="E20" s="3">
-        <v>7400</v>
+        <v>-3300</v>
       </c>
       <c r="F20" s="3">
-        <v>11500</v>
+        <v>-1900</v>
       </c>
       <c r="G20" s="3">
-        <v>5400</v>
+        <v>-500</v>
       </c>
       <c r="H20" s="3">
-        <v>17500</v>
+        <v>-600</v>
       </c>
       <c r="I20" s="3">
-        <v>3900</v>
+        <v>-3800</v>
       </c>
       <c r="J20" s="3">
-        <v>12200</v>
+        <v>0</v>
       </c>
       <c r="K20" s="3">
         <v>6700</v>
@@ -1231,25 +1231,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>72000</v>
+        <v>69400</v>
       </c>
       <c r="E21" s="3">
-        <v>-49500</v>
+        <v>-30700</v>
       </c>
       <c r="F21" s="3">
-        <v>46500</v>
+        <v>43800</v>
       </c>
       <c r="G21" s="3">
-        <v>59700</v>
+        <v>59500</v>
       </c>
       <c r="H21" s="3">
-        <v>94300</v>
+        <v>79300</v>
       </c>
       <c r="I21" s="3">
-        <v>78700</v>
+        <v>81700</v>
       </c>
       <c r="J21" s="3">
-        <v>68100</v>
+        <v>66800</v>
       </c>
       <c r="K21" s="3">
         <v>55000</v>
@@ -1279,10 +1279,10 @@
         <v>2000</v>
       </c>
       <c r="E22" s="3">
-        <v>3900</v>
+        <v>4100</v>
       </c>
       <c r="F22" s="3">
-        <v>2200</v>
+        <v>2400</v>
       </c>
       <c r="G22" s="3">
         <v>500</v>
@@ -1321,25 +1321,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>53600</v>
+        <v>53400</v>
       </c>
       <c r="E23" s="3">
-        <v>-71100</v>
+        <v>-73300</v>
       </c>
       <c r="F23" s="3">
-        <v>27600</v>
+        <v>30800</v>
       </c>
       <c r="G23" s="3">
-        <v>49900</v>
+        <v>54400</v>
       </c>
       <c r="H23" s="3">
-        <v>88300</v>
+        <v>90100</v>
       </c>
       <c r="I23" s="3">
-        <v>75000</v>
+        <v>76200</v>
       </c>
       <c r="J23" s="3">
-        <v>64400</v>
+        <v>70000</v>
       </c>
       <c r="K23" s="3">
         <v>50100</v>
@@ -1369,22 +1369,22 @@
         <v>16700</v>
       </c>
       <c r="E24" s="3">
-        <v>-6200</v>
+        <v>-6400</v>
       </c>
       <c r="F24" s="3">
-        <v>15800</v>
+        <v>17700</v>
       </c>
       <c r="G24" s="3">
-        <v>15600</v>
+        <v>16900</v>
       </c>
       <c r="H24" s="3">
-        <v>26700</v>
+        <v>27200</v>
       </c>
       <c r="I24" s="3">
-        <v>21500</v>
+        <v>22200</v>
       </c>
       <c r="J24" s="3">
-        <v>25700</v>
+        <v>28100</v>
       </c>
       <c r="K24" s="3">
         <v>11700</v>
@@ -1456,25 +1456,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>36900</v>
+        <v>36700</v>
       </c>
       <c r="E26" s="3">
-        <v>-64900</v>
+        <v>-66900</v>
       </c>
       <c r="F26" s="3">
-        <v>11700</v>
+        <v>13200</v>
       </c>
       <c r="G26" s="3">
-        <v>34400</v>
+        <v>37500</v>
       </c>
       <c r="H26" s="3">
-        <v>61500</v>
+        <v>62900</v>
       </c>
       <c r="I26" s="3">
-        <v>53500</v>
+        <v>54000</v>
       </c>
       <c r="J26" s="3">
-        <v>38600</v>
+        <v>42000</v>
       </c>
       <c r="K26" s="3">
         <v>38400</v>
@@ -1504,22 +1504,22 @@
         <v>38000</v>
       </c>
       <c r="E27" s="3">
-        <v>-59900</v>
+        <v>-61600</v>
       </c>
       <c r="F27" s="3">
-        <v>12500</v>
+        <v>14000</v>
       </c>
       <c r="G27" s="3">
-        <v>36800</v>
+        <v>40000</v>
       </c>
       <c r="H27" s="3">
-        <v>62400</v>
+        <v>63600</v>
       </c>
       <c r="I27" s="3">
-        <v>52400</v>
+        <v>54000</v>
       </c>
       <c r="J27" s="3">
-        <v>38600</v>
+        <v>42000</v>
       </c>
       <c r="K27" s="3">
         <v>37000</v>
@@ -1726,25 +1726,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-8300</v>
+        <v>3000</v>
       </c>
       <c r="E32" s="3">
-        <v>-7400</v>
+        <v>3300</v>
       </c>
       <c r="F32" s="3">
-        <v>-11500</v>
+        <v>1900</v>
       </c>
       <c r="G32" s="3">
-        <v>-5400</v>
+        <v>500</v>
       </c>
       <c r="H32" s="3">
-        <v>-17500</v>
+        <v>600</v>
       </c>
       <c r="I32" s="3">
-        <v>-3900</v>
+        <v>3800</v>
       </c>
       <c r="J32" s="3">
-        <v>-12200</v>
+        <v>0</v>
       </c>
       <c r="K32" s="3">
         <v>-6700</v>
@@ -1774,22 +1774,22 @@
         <v>38000</v>
       </c>
       <c r="E33" s="3">
-        <v>-59900</v>
+        <v>-61600</v>
       </c>
       <c r="F33" s="3">
-        <v>12500</v>
+        <v>14000</v>
       </c>
       <c r="G33" s="3">
-        <v>36800</v>
+        <v>40000</v>
       </c>
       <c r="H33" s="3">
-        <v>62400</v>
+        <v>63600</v>
       </c>
       <c r="I33" s="3">
-        <v>52400</v>
+        <v>54000</v>
       </c>
       <c r="J33" s="3">
-        <v>38600</v>
+        <v>42000</v>
       </c>
       <c r="K33" s="3">
         <v>37000</v>
@@ -1864,22 +1864,22 @@
         <v>38000</v>
       </c>
       <c r="E35" s="3">
-        <v>-59900</v>
+        <v>-61600</v>
       </c>
       <c r="F35" s="3">
-        <v>12500</v>
+        <v>14000</v>
       </c>
       <c r="G35" s="3">
-        <v>36800</v>
+        <v>40000</v>
       </c>
       <c r="H35" s="3">
-        <v>62400</v>
+        <v>63600</v>
       </c>
       <c r="I35" s="3">
-        <v>52400</v>
+        <v>54000</v>
       </c>
       <c r="J35" s="3">
-        <v>38600</v>
+        <v>42000</v>
       </c>
       <c r="K35" s="3">
         <v>37000</v>
@@ -1994,25 +1994,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>107900</v>
+        <v>108000</v>
       </c>
       <c r="E41" s="3">
-        <v>98600</v>
+        <v>101400</v>
       </c>
       <c r="F41" s="3">
-        <v>42100</v>
+        <v>47000</v>
       </c>
       <c r="G41" s="3">
-        <v>86200</v>
+        <v>93600</v>
       </c>
       <c r="H41" s="3">
-        <v>45100</v>
+        <v>45900</v>
       </c>
       <c r="I41" s="3">
-        <v>178200</v>
+        <v>183800</v>
       </c>
       <c r="J41" s="3">
-        <v>22800</v>
+        <v>24900</v>
       </c>
       <c r="K41" s="3">
         <v>124700</v>
@@ -2039,25 +2039,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>62600</v>
+        <v>64900</v>
       </c>
       <c r="E42" s="3">
-        <v>32100</v>
+        <v>35400</v>
       </c>
       <c r="F42" s="3">
-        <v>100900</v>
+        <v>114400</v>
       </c>
       <c r="G42" s="3">
-        <v>76700</v>
+        <v>83400</v>
       </c>
       <c r="H42" s="3">
-        <v>90800</v>
+        <v>92500</v>
       </c>
       <c r="I42" s="3">
-        <v>140000</v>
+        <v>144400</v>
       </c>
       <c r="J42" s="3">
-        <v>153600</v>
+        <v>167500</v>
       </c>
       <c r="K42" s="3">
         <v>38000</v>
@@ -2084,25 +2084,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>40500</v>
+        <v>47900</v>
       </c>
       <c r="E43" s="3">
-        <v>105400</v>
+        <v>114100</v>
       </c>
       <c r="F43" s="3">
-        <v>99100</v>
+        <v>119900</v>
       </c>
       <c r="G43" s="3">
-        <v>47000</v>
+        <v>51100</v>
       </c>
       <c r="H43" s="3">
-        <v>30100</v>
+        <v>30700</v>
       </c>
       <c r="I43" s="3">
-        <v>27800</v>
+        <v>19200</v>
       </c>
       <c r="J43" s="3">
-        <v>9000</v>
+        <v>9800</v>
       </c>
       <c r="K43" s="3">
         <v>25800</v>
@@ -2132,13 +2132,13 @@
         <v>2900</v>
       </c>
       <c r="E44" s="3">
-        <v>3100</v>
+        <v>3200</v>
       </c>
       <c r="F44" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="G44" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="H44" s="3">
         <v>400</v>
@@ -2147,7 +2147,7 @@
         <v>400</v>
       </c>
       <c r="J44" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="K44" s="3">
         <v>300</v>
@@ -2174,25 +2174,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>15500</v>
+        <v>4900</v>
       </c>
       <c r="E45" s="3">
-        <v>16700</v>
+        <v>7900</v>
       </c>
       <c r="F45" s="3">
-        <v>15800</v>
+        <v>3700</v>
       </c>
       <c r="G45" s="3">
-        <v>12900</v>
+        <v>11900</v>
       </c>
       <c r="H45" s="3">
-        <v>12000</v>
+        <v>9500</v>
       </c>
       <c r="I45" s="3">
-        <v>8200</v>
+        <v>7800</v>
       </c>
       <c r="J45" s="3">
-        <v>23700</v>
+        <v>19600</v>
       </c>
       <c r="K45" s="3">
         <v>33800</v>
@@ -2219,25 +2219,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>229300</v>
+        <v>229400</v>
       </c>
       <c r="E46" s="3">
-        <v>255800</v>
+        <v>263100</v>
       </c>
       <c r="F46" s="3">
-        <v>258200</v>
+        <v>288300</v>
       </c>
       <c r="G46" s="3">
-        <v>223400</v>
+        <v>242700</v>
       </c>
       <c r="H46" s="3">
-        <v>178400</v>
+        <v>181700</v>
       </c>
       <c r="I46" s="3">
-        <v>345500</v>
+        <v>356300</v>
       </c>
       <c r="J46" s="3">
-        <v>209400</v>
+        <v>228300</v>
       </c>
       <c r="K46" s="3">
         <v>222600</v>
@@ -2264,25 +2264,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>62400</v>
+        <v>26100</v>
       </c>
       <c r="E47" s="3">
-        <v>84800</v>
+        <v>25600</v>
       </c>
       <c r="F47" s="3">
-        <v>91000</v>
+        <v>34400</v>
       </c>
       <c r="G47" s="3">
-        <v>146500</v>
+        <v>131700</v>
       </c>
       <c r="H47" s="3">
-        <v>152300</v>
+        <v>137700</v>
       </c>
       <c r="I47" s="3">
-        <v>60300</v>
+        <v>25000</v>
       </c>
       <c r="J47" s="3">
-        <v>17600</v>
+        <v>18800</v>
       </c>
       <c r="K47" s="3">
         <v>4900</v>
@@ -2309,25 +2309,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>331300</v>
+        <v>331500</v>
       </c>
       <c r="E48" s="3">
-        <v>360600</v>
+        <v>370800</v>
       </c>
       <c r="F48" s="3">
-        <v>147400</v>
+        <v>164600</v>
       </c>
       <c r="G48" s="3">
-        <v>94300</v>
+        <v>102400</v>
       </c>
       <c r="H48" s="3">
-        <v>86700</v>
+        <v>88300</v>
       </c>
       <c r="I48" s="3">
-        <v>62700</v>
+        <v>32300</v>
       </c>
       <c r="J48" s="3">
-        <v>13600</v>
+        <v>14900</v>
       </c>
       <c r="K48" s="3">
         <v>15400</v>
@@ -2357,22 +2357,22 @@
         <v>41600</v>
       </c>
       <c r="E49" s="3">
-        <v>44100</v>
+        <v>48800</v>
       </c>
       <c r="F49" s="3">
-        <v>90400</v>
+        <v>100900</v>
       </c>
       <c r="G49" s="3">
-        <v>83400</v>
+        <v>90600</v>
       </c>
       <c r="H49" s="3">
-        <v>84100</v>
+        <v>85600</v>
       </c>
       <c r="I49" s="3">
-        <v>8500</v>
+        <v>4800</v>
       </c>
       <c r="J49" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="K49" s="3">
         <v>1100</v>
@@ -2489,25 +2489,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>49700</v>
+        <v>42000</v>
       </c>
       <c r="E52" s="3">
-        <v>52700</v>
+        <v>56000</v>
       </c>
       <c r="F52" s="3">
-        <v>71100</v>
+        <v>75300</v>
       </c>
       <c r="G52" s="3">
-        <v>29800</v>
+        <v>13600</v>
       </c>
       <c r="H52" s="3">
-        <v>36600</v>
+        <v>14300</v>
       </c>
       <c r="I52" s="3">
-        <v>22900</v>
+        <v>4200</v>
       </c>
       <c r="J52" s="3">
-        <v>5900</v>
+        <v>1700</v>
       </c>
       <c r="K52" s="3">
         <v>16800</v>
@@ -2579,25 +2579,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>714300</v>
+        <v>714500</v>
       </c>
       <c r="E54" s="3">
-        <v>801300</v>
+        <v>824100</v>
       </c>
       <c r="F54" s="3">
-        <v>658000</v>
+        <v>734700</v>
       </c>
       <c r="G54" s="3">
-        <v>577300</v>
+        <v>627200</v>
       </c>
       <c r="H54" s="3">
-        <v>538000</v>
+        <v>548100</v>
       </c>
       <c r="I54" s="3">
-        <v>434200</v>
+        <v>447800</v>
       </c>
       <c r="J54" s="3">
-        <v>247600</v>
+        <v>269900</v>
       </c>
       <c r="K54" s="3">
         <v>260800</v>
@@ -2662,16 +2662,16 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>10300</v>
+        <v>10800</v>
       </c>
       <c r="E57" s="3">
-        <v>17400</v>
+        <v>18200</v>
       </c>
       <c r="F57" s="3">
-        <v>3400</v>
+        <v>4200</v>
       </c>
       <c r="G57" s="3">
-        <v>2800</v>
+        <v>3200</v>
       </c>
       <c r="H57" s="3">
         <v>2200</v>
@@ -2680,7 +2680,7 @@
         <v>1300</v>
       </c>
       <c r="J57" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="K57" s="3">
         <v>1100</v>
@@ -2707,25 +2707,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>16500</v>
+        <v>54200</v>
       </c>
       <c r="E58" s="3">
-        <v>42000</v>
+        <v>82800</v>
       </c>
       <c r="F58" s="3">
-        <v>57300</v>
+        <v>63900</v>
       </c>
       <c r="G58" s="3">
-        <v>21100</v>
+        <v>23000</v>
       </c>
       <c r="H58" s="3">
-        <v>8500</v>
+        <v>8600</v>
       </c>
       <c r="I58" s="3">
-        <v>16900</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+        <v>8700</v>
+      </c>
+      <c r="J58" s="3">
+        <v>0</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2752,25 +2752,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>162300</v>
+        <v>92000</v>
       </c>
       <c r="E59" s="3">
-        <v>241300</v>
+        <v>89500</v>
       </c>
       <c r="F59" s="3">
-        <v>115600</v>
+        <v>96000</v>
       </c>
       <c r="G59" s="3">
-        <v>98700</v>
+        <v>83600</v>
       </c>
       <c r="H59" s="3">
-        <v>101500</v>
+        <v>87000</v>
       </c>
       <c r="I59" s="3">
-        <v>182400</v>
+        <v>78000</v>
       </c>
       <c r="J59" s="3">
-        <v>92400</v>
+        <v>81400</v>
       </c>
       <c r="K59" s="3">
         <v>67300</v>
@@ -2797,25 +2797,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>189100</v>
+        <v>189200</v>
       </c>
       <c r="E60" s="3">
-        <v>217700</v>
+        <v>223900</v>
       </c>
       <c r="F60" s="3">
-        <v>176200</v>
+        <v>196800</v>
       </c>
       <c r="G60" s="3">
-        <v>122600</v>
+        <v>133200</v>
       </c>
       <c r="H60" s="3">
-        <v>112100</v>
+        <v>114200</v>
       </c>
       <c r="I60" s="3">
-        <v>100100</v>
+        <v>103200</v>
       </c>
       <c r="J60" s="3">
-        <v>93500</v>
+        <v>101900</v>
       </c>
       <c r="K60" s="3">
         <v>68300</v>
@@ -2842,13 +2842,13 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>8000</v>
+        <v>204300</v>
       </c>
       <c r="E61" s="3">
-        <v>22600</v>
+        <v>243000</v>
       </c>
       <c r="F61" s="3">
-        <v>42500</v>
+        <v>47500</v>
       </c>
       <c r="G61" s="3">
         <v>0</v>
@@ -2887,25 +2887,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>308500</v>
+        <v>69600</v>
       </c>
       <c r="E62" s="3">
-        <v>327300</v>
+        <v>69300</v>
       </c>
       <c r="F62" s="3">
-        <v>151200</v>
+        <v>83400</v>
       </c>
       <c r="G62" s="3">
-        <v>137500</v>
+        <v>66700</v>
       </c>
       <c r="H62" s="3">
-        <v>141500</v>
+        <v>57100</v>
       </c>
       <c r="I62" s="3">
-        <v>152800</v>
+        <v>41700</v>
       </c>
       <c r="J62" s="3">
-        <v>50800</v>
+        <v>32300</v>
       </c>
       <c r="K62" s="3">
         <v>49700</v>
@@ -3067,25 +3067,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>511000</v>
+        <v>505800</v>
       </c>
       <c r="E66" s="3">
-        <v>574100</v>
+        <v>583600</v>
       </c>
       <c r="F66" s="3">
-        <v>396100</v>
+        <v>413100</v>
       </c>
       <c r="G66" s="3">
-        <v>280800</v>
+        <v>282600</v>
       </c>
       <c r="H66" s="3">
-        <v>275700</v>
+        <v>258300</v>
       </c>
       <c r="I66" s="3">
-        <v>201400</v>
+        <v>206500</v>
       </c>
       <c r="J66" s="3">
-        <v>144300</v>
+        <v>157300</v>
       </c>
       <c r="K66" s="3">
         <v>118100</v>
@@ -3310,26 +3310,26 @@
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
-        <v>-80100</v>
-      </c>
-      <c r="E72" s="3">
-        <v>-115300</v>
+      <c r="D72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F72" s="3">
-        <v>46000</v>
+        <v>51400</v>
       </c>
       <c r="G72" s="3">
-        <v>80400</v>
+        <v>87300</v>
       </c>
       <c r="H72" s="3">
-        <v>43500</v>
+        <v>44300</v>
       </c>
       <c r="I72" s="3">
-        <v>35600</v>
+        <v>36700</v>
       </c>
       <c r="J72" s="3">
-        <v>31500</v>
+        <v>34300</v>
       </c>
       <c r="K72" s="3">
         <v>77400</v>
@@ -3491,25 +3491,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>203300</v>
+        <v>203400</v>
       </c>
       <c r="E76" s="3">
-        <v>227200</v>
+        <v>233700</v>
       </c>
       <c r="F76" s="3">
-        <v>261900</v>
+        <v>292400</v>
       </c>
       <c r="G76" s="3">
-        <v>296500</v>
+        <v>322100</v>
       </c>
       <c r="H76" s="3">
-        <v>262400</v>
+        <v>267300</v>
       </c>
       <c r="I76" s="3">
-        <v>232800</v>
+        <v>240000</v>
       </c>
       <c r="J76" s="3">
-        <v>103200</v>
+        <v>112500</v>
       </c>
       <c r="K76" s="3">
         <v>142700</v>
@@ -3634,22 +3634,22 @@
         <v>38000</v>
       </c>
       <c r="E81" s="3">
-        <v>-59900</v>
+        <v>-61600</v>
       </c>
       <c r="F81" s="3">
-        <v>12500</v>
+        <v>14000</v>
       </c>
       <c r="G81" s="3">
-        <v>36800</v>
+        <v>40000</v>
       </c>
       <c r="H81" s="3">
-        <v>62400</v>
+        <v>63600</v>
       </c>
       <c r="I81" s="3">
-        <v>52400</v>
+        <v>54000</v>
       </c>
       <c r="J81" s="3">
-        <v>38600</v>
+        <v>42000</v>
       </c>
       <c r="K81" s="3">
         <v>37000</v>
@@ -3695,25 +3695,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>16500</v>
+        <v>15500</v>
       </c>
       <c r="E83" s="3">
-        <v>17700</v>
+        <v>17300</v>
       </c>
       <c r="F83" s="3">
-        <v>16800</v>
+        <v>18000</v>
       </c>
       <c r="G83" s="3">
-        <v>9300</v>
+        <v>9100</v>
       </c>
       <c r="H83" s="3">
-        <v>5700</v>
+        <v>5400</v>
       </c>
       <c r="I83" s="3">
-        <v>3600</v>
+        <v>3500</v>
       </c>
       <c r="J83" s="3">
-        <v>3500</v>
+        <v>3700</v>
       </c>
       <c r="K83" s="3">
         <v>4900</v>
@@ -3968,22 +3968,22 @@
         <v>64200</v>
       </c>
       <c r="E89" s="3">
-        <v>41500</v>
+        <v>42700</v>
       </c>
       <c r="F89" s="3">
-        <v>53500</v>
+        <v>59700</v>
       </c>
       <c r="G89" s="3">
-        <v>41600</v>
+        <v>45200</v>
       </c>
       <c r="H89" s="3">
-        <v>72500</v>
+        <v>73800</v>
       </c>
       <c r="I89" s="3">
-        <v>78200</v>
+        <v>80700</v>
       </c>
       <c r="J89" s="3">
-        <v>66200</v>
+        <v>72200</v>
       </c>
       <c r="K89" s="3">
         <v>61700</v>
@@ -4032,22 +4032,22 @@
         <v>-12400</v>
       </c>
       <c r="E91" s="3">
-        <v>-11800</v>
+        <v>-12100</v>
       </c>
       <c r="F91" s="3">
-        <v>-82000</v>
+        <v>-91600</v>
       </c>
       <c r="G91" s="3">
-        <v>-15800</v>
+        <v>-17100</v>
       </c>
       <c r="H91" s="3">
-        <v>-30100</v>
+        <v>-30600</v>
       </c>
       <c r="I91" s="3">
-        <v>-19500</v>
+        <v>-20100</v>
       </c>
       <c r="J91" s="3">
-        <v>-2300</v>
+        <v>-2500</v>
       </c>
       <c r="K91" s="3">
         <v>-800</v>
@@ -4167,22 +4167,22 @@
         <v>-13200</v>
       </c>
       <c r="E94" s="3">
-        <v>59300</v>
+        <v>61000</v>
       </c>
       <c r="F94" s="3">
-        <v>-137900</v>
+        <v>-154000</v>
       </c>
       <c r="G94" s="3">
-        <v>-15700</v>
+        <v>-17100</v>
       </c>
       <c r="H94" s="3">
-        <v>-172000</v>
+        <v>-175200</v>
       </c>
       <c r="I94" s="3">
-        <v>-25600</v>
+        <v>-26400</v>
       </c>
       <c r="J94" s="3">
-        <v>-105000</v>
+        <v>-114500</v>
       </c>
       <c r="K94" s="3">
         <v>10300</v>
@@ -4231,22 +4231,22 @@
         <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>-5800</v>
+        <v>5900</v>
       </c>
       <c r="F96" s="3">
-        <v>-45100</v>
+        <v>50400</v>
       </c>
       <c r="G96" s="3">
         <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>-32000</v>
+        <v>32600</v>
       </c>
       <c r="I96" s="3">
-        <v>-28300</v>
+        <v>29200</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>89000</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4411,22 +4411,22 @@
         <v>-42800</v>
       </c>
       <c r="E100" s="3">
-        <v>-47300</v>
+        <v>-48600</v>
       </c>
       <c r="F100" s="3">
-        <v>33900</v>
+        <v>37800</v>
       </c>
       <c r="G100" s="3">
-        <v>16300</v>
+        <v>17700</v>
       </c>
       <c r="H100" s="3">
-        <v>-29900</v>
+        <v>-30500</v>
       </c>
       <c r="I100" s="3">
-        <v>93500</v>
+        <v>96400</v>
       </c>
       <c r="J100" s="3">
-        <v>-91000</v>
+        <v>-99200</v>
       </c>
       <c r="K100" s="3">
         <v>-18500</v>
@@ -4462,13 +4462,13 @@
         <v>-200</v>
       </c>
       <c r="G101" s="3">
-        <v>-1100</v>
+        <v>-1200</v>
       </c>
       <c r="H101" s="3">
         <v>-1000</v>
       </c>
       <c r="I101" s="3">
-        <v>9300</v>
+        <v>9600</v>
       </c>
       <c r="J101" s="3">
         <v>-200</v>
@@ -4501,22 +4501,22 @@
         <v>8100</v>
       </c>
       <c r="E102" s="3">
-        <v>53700</v>
+        <v>55200</v>
       </c>
       <c r="F102" s="3">
-        <v>-50700</v>
+        <v>-56700</v>
       </c>
       <c r="G102" s="3">
-        <v>41100</v>
+        <v>44700</v>
       </c>
       <c r="H102" s="3">
-        <v>-130400</v>
+        <v>-132900</v>
       </c>
       <c r="I102" s="3">
-        <v>155400</v>
+        <v>160300</v>
       </c>
       <c r="J102" s="3">
-        <v>-130000</v>
+        <v>-141700</v>
       </c>
       <c r="K102" s="3">
         <v>54300</v>

--- a/AAII_Financials/Yearly/GHG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/GHG_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="92">
   <si>
     <t>GHG</t>
   </si>
@@ -656,61 +656,61 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
@@ -720,42 +720,45 @@
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>184100</v>
+      </c>
+      <c r="E8" s="3">
         <v>229500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>213000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>309800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>142500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>156800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>131700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>114200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>90100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>91200</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
@@ -765,42 +768,45 @@
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>112700</v>
+      </c>
+      <c r="E9" s="3">
         <v>133600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>154600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>206600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>61500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>48700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>39900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>34900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>9200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>11300</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
@@ -810,42 +816,45 @@
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>71400</v>
+      </c>
+      <c r="E10" s="3">
         <v>95900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>58400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>103200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>80900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>108100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>91800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>79400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>80800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>79900</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
@@ -855,9 +864,12 @@
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -875,8 +887,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -919,9 +932,12 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -964,42 +980,45 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>3300</v>
+        <v>11600</v>
       </c>
       <c r="E14" s="3">
-        <v>27400</v>
+        <v>3600</v>
       </c>
       <c r="F14" s="3">
+        <v>26300</v>
+      </c>
+      <c r="G14" s="3">
         <v>1300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>5600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-7400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>8900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-3200</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>1000</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1009,42 +1028,45 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E15" s="3">
         <v>16500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>18200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>18800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>10100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>5800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>3700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>3800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>200</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1054,9 +1076,12 @@
       <c r="P15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1071,41 +1096,42 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>179600</v>
+        <v>152400</v>
       </c>
       <c r="E17" s="3">
-        <v>265200</v>
+        <v>179300</v>
       </c>
       <c r="F17" s="3">
+        <v>266300</v>
+      </c>
+      <c r="G17" s="3">
         <v>286700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>93600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>83800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>57500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>51300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>46600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>49800</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1115,42 +1141,45 @@
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>49900</v>
+        <v>31700</v>
       </c>
       <c r="E18" s="3">
-        <v>-52200</v>
+        <v>50200</v>
       </c>
       <c r="F18" s="3">
+        <v>-53300</v>
+      </c>
+      <c r="G18" s="3">
         <v>23100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>48900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>73000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>74200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>62900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>43400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>41300</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1160,9 +1189,12 @@
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1180,41 +1212,42 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-3000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-3300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-3800</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>6700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>6500</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1224,42 +1257,45 @@
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>69400</v>
+        <v>49600</v>
       </c>
       <c r="E21" s="3">
-        <v>-30700</v>
+        <v>69700</v>
       </c>
       <c r="F21" s="3">
+        <v>-31800</v>
+      </c>
+      <c r="G21" s="3">
         <v>43800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>59500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>79300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>81700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>66800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>55000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>53800</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1269,41 +1305,44 @@
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>900</v>
+      </c>
+      <c r="E22" s="3">
         <v>2000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>4100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>2400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>200</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
       <c r="L22" s="3">
         <v>0</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
+      <c r="M22" s="3">
+        <v>0</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>3</v>
@@ -1314,42 +1353,45 @@
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>26900</v>
+      </c>
+      <c r="E23" s="3">
         <v>53400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-73300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>30800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>54400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>90100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>76200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>70000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>50100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>47800</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1359,42 +1401,45 @@
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E24" s="3">
         <v>16700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-6400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>17700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>16900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>27200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>22200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>28100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>11700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>11500</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1404,9 +1449,12 @@
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1449,42 +1497,45 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>14700</v>
+      </c>
+      <c r="E26" s="3">
         <v>36700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-66900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>13200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>37500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>62900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>54000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>42000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>38400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>36300</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1494,42 +1545,45 @@
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E27" s="3">
         <v>38000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-61600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>14000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>40000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>63600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>54000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>42000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>37000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>33900</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1539,9 +1593,12 @@
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1584,9 +1641,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1629,9 +1689,12 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1674,9 +1737,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1719,42 +1785,45 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E32" s="3">
         <v>3000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>3300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>3800</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-6700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-6500</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1764,42 +1833,45 @@
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E33" s="3">
         <v>38000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-61600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>14000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>40000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>63600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>54000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>42000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>37000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>33900</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1809,9 +1881,12 @@
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1854,42 +1929,45 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E35" s="3">
         <v>38000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-61600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>14000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>40000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>63600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>54000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>42000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>37000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>33900</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1899,47 +1977,50 @@
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1949,9 +2030,12 @@
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1969,8 +2053,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1988,41 +2073,42 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>204200</v>
+      </c>
+      <c r="E41" s="3">
         <v>108000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>101400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>47000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>93600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>45900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>183800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>24900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>124700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>72700</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2032,42 +2118,45 @@
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E42" s="3">
         <v>64900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>35400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>114400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>83400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>92500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>144400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>167500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>38000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>57200</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2077,42 +2166,45 @@
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>35400</v>
+      </c>
+      <c r="E43" s="3">
         <v>47900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>114100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>119900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>51100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>30700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>19200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>9800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>25800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>17100</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2122,26 +2214,29 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>900</v>
+      </c>
+      <c r="E44" s="3">
         <v>2900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>3200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>600</v>
-      </c>
-      <c r="H44" s="3">
-        <v>400</v>
       </c>
       <c r="I44" s="3">
         <v>400</v>
@@ -2150,13 +2245,13 @@
         <v>400</v>
       </c>
       <c r="K44" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="L44" s="3">
         <v>300</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>3</v>
+      <c r="M44" s="3">
+        <v>300</v>
       </c>
       <c r="N44" s="3" t="s">
         <v>3</v>
@@ -2167,42 +2262,45 @@
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E45" s="3">
         <v>4900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>7900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>11900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>9500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>7800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>19600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>33800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>15200</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2212,42 +2310,45 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>251400</v>
+      </c>
+      <c r="E46" s="3">
         <v>229400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>263100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>288300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>242700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>181700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>356300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>228300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>222600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>162500</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2257,42 +2358,45 @@
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>25200</v>
+      </c>
+      <c r="E47" s="3">
         <v>26100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>25600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>34400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>131700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>137700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>25000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>18800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>4900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>11700</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2302,42 +2406,45 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>271000</v>
+      </c>
+      <c r="E48" s="3">
         <v>331500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>370800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>164600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>102400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>88300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>32300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>14900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>15400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>20300</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2347,42 +2454,45 @@
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>23500</v>
+      </c>
+      <c r="E49" s="3">
         <v>41600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>48800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>100900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>90600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>85600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1300</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2392,9 +2502,12 @@
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2437,9 +2550,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2482,42 +2598,45 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>70800</v>
+      </c>
+      <c r="E52" s="3">
         <v>42000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>56000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>75300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>13600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>14300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>16800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>6300</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2527,9 +2646,12 @@
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2572,42 +2694,45 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>677800</v>
+      </c>
+      <c r="E54" s="3">
         <v>714500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>824100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>734700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>627200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>548100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>447800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>269900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>260800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>202100</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2617,9 +2742,12 @@
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2637,8 +2765,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2656,31 +2785,32 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E57" s="3">
         <v>10800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>18200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1300</v>
-      </c>
-      <c r="J57" s="3">
-        <v>1100</v>
       </c>
       <c r="K57" s="3">
         <v>1100</v>
@@ -2688,8 +2818,8 @@
       <c r="L57" s="3">
         <v>1100</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
+      <c r="M57" s="3">
+        <v>1100</v>
       </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
@@ -2700,35 +2830,38 @@
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>33100</v>
+      </c>
+      <c r="E58" s="3">
         <v>54200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>82800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>63900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>23000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>8600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>8700</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
+      <c r="K58" s="3">
+        <v>0</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
@@ -2742,45 +2875,48 @@
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>85800</v>
+      </c>
+      <c r="E59" s="3">
         <v>92000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>89500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>96000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>83600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>87000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>78000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>81400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>67300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>51500</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2790,42 +2926,45 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>159700</v>
+      </c>
+      <c r="E60" s="3">
         <v>189200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>223900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>196800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>133200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>114200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>103200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>101900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>68300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>52500</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2835,24 +2974,27 @@
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>201700</v>
+      </c>
+      <c r="E61" s="3">
         <v>204300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>243000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>47500</v>
       </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
       <c r="H61" s="3">
         <v>0</v>
       </c>
@@ -2880,42 +3022,45 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>76900</v>
+      </c>
+      <c r="E62" s="3">
         <v>69600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>69300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>83400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>66700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>57100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>41700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>32300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>49700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>37900</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2925,9 +3070,12 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2970,9 +3118,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3015,9 +3166,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3060,42 +3214,45 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>473300</v>
+      </c>
+      <c r="E66" s="3">
         <v>505800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>583600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>413100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>282600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>258300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>206500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>157300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>118100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>90600</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3105,9 +3262,12 @@
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3125,8 +3285,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3169,9 +3330,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3214,9 +3378,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3259,9 +3426,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3304,9 +3474,12 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -3317,29 +3490,29 @@
         <v>3</v>
       </c>
       <c r="F72" s="3">
+        <v>-118500</v>
+      </c>
+      <c r="G72" s="3">
         <v>51400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>87300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>44300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>36700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>34300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>77400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>44300</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3349,9 +3522,12 @@
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3394,9 +3570,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3439,9 +3618,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3484,42 +3666,45 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>199900</v>
+      </c>
+      <c r="E76" s="3">
         <v>203400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>233700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>292400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>322100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>267300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>240000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>112500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>142700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>111500</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3529,9 +3714,12 @@
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3574,47 +3762,50 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3624,42 +3815,45 @@
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E81" s="3">
         <v>38000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-61600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>14000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>40000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>63600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>54000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>42000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>37000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>33900</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3669,9 +3863,12 @@
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3689,41 +3886,42 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E83" s="3">
         <v>15500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>17300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>18000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>9100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>5400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>4900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>6000</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3733,9 +3931,12 @@
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3778,9 +3979,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3823,9 +4027,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3868,9 +4075,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3913,9 +4123,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3958,42 +4171,45 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>51200</v>
+      </c>
+      <c r="E89" s="3">
         <v>64200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>42700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>59700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>45200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>73800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>80700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>72200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>61700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>51300</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4003,9 +4219,12 @@
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4023,41 +4242,42 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-12400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-12100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-91600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-17100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-30600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-20100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1900</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
@@ -4067,9 +4287,12 @@
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4112,9 +4335,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4157,42 +4383,45 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>47300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-13200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>61000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-154000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-17100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-175200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-26400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-114500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>10300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-26800</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4202,9 +4431,12 @@
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4222,35 +4454,36 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>9700</v>
       </c>
       <c r="E96" s="3">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3">
         <v>5900</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>50400</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
       <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
         <v>32600</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>29200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>89000</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
@@ -4266,9 +4499,12 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4311,9 +4547,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4356,9 +4595,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4401,42 +4643,45 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-42800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-48600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>37800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>17700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-30500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>96400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-99200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-18500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-7400</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4446,42 +4691,45 @@
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
         <v>200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>9600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>800</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
@@ -4491,42 +4739,45 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>100500</v>
+      </c>
+      <c r="E102" s="3">
         <v>8100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>55200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-56700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>44700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-132900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>160300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-141700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>54300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>17900</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4536,7 +4787,10 @@
       <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/GHG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/GHG_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="92">
   <si>
     <t>GHG</t>
   </si>
@@ -3483,11 +3483,11 @@
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>3</v>
+      <c r="D72" s="3">
+        <v>-62800</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-80200</v>
       </c>
       <c r="F72" s="3">
         <v>-118500</v>

--- a/AAII_Financials/Yearly/GHG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/GHG_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="92">
   <si>
     <t>GHG</t>
   </si>
@@ -656,64 +656,64 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
@@ -723,45 +723,48 @@
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>156900</v>
+      </c>
+      <c r="E8" s="3">
         <v>184100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>229500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>213000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>309800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>142500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>156800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>131700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>114200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>90100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>91200</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
@@ -771,45 +774,48 @@
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>102100</v>
+      </c>
+      <c r="E9" s="3">
         <v>112700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>133600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>154600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>206600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>61500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>48700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>39900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>34900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>9200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>11300</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
@@ -819,45 +825,48 @@
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>54800</v>
+      </c>
+      <c r="E10" s="3">
         <v>71400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>95900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>58400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>103200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>80900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>108100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>91800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>79400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>80800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>79900</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
@@ -867,9 +876,12 @@
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -888,8 +900,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -935,9 +948,12 @@
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -983,45 +999,48 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>11600</v>
+        <v>-4300</v>
       </c>
       <c r="E14" s="3">
-        <v>3600</v>
+        <v>18400</v>
       </c>
       <c r="F14" s="3">
-        <v>26300</v>
+        <v>3200</v>
       </c>
       <c r="G14" s="3">
+        <v>25600</v>
+      </c>
+      <c r="H14" s="3">
         <v>1300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>5600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-7400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>8900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-3200</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>1000</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1031,45 +1050,48 @@
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E15" s="3">
         <v>15900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>16500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>18200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>18800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>10100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>5800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>3700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>3800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>200</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1079,9 +1101,12 @@
       <c r="Q15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1097,44 +1122,45 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>152400</v>
+        <v>136000</v>
       </c>
       <c r="E17" s="3">
-        <v>179300</v>
+        <v>145500</v>
       </c>
       <c r="F17" s="3">
-        <v>266300</v>
+        <v>179700</v>
       </c>
       <c r="G17" s="3">
+        <v>266900</v>
+      </c>
+      <c r="H17" s="3">
         <v>286700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>93600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>83800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>57500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>51300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>46600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>49800</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1144,45 +1170,48 @@
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>31700</v>
+        <v>20900</v>
       </c>
       <c r="E18" s="3">
-        <v>50200</v>
+        <v>38600</v>
       </c>
       <c r="F18" s="3">
-        <v>-53300</v>
+        <v>49800</v>
       </c>
       <c r="G18" s="3">
+        <v>-53900</v>
+      </c>
+      <c r="H18" s="3">
         <v>23100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>48900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>73000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>74200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>62900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>43400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>41300</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1192,9 +1221,12 @@
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1213,44 +1245,45 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E20" s="3">
         <v>-2100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-3000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-3300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-3800</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>6700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>6500</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1260,45 +1293,48 @@
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>49600</v>
+        <v>34100</v>
       </c>
       <c r="E21" s="3">
-        <v>69700</v>
+        <v>56500</v>
       </c>
       <c r="F21" s="3">
-        <v>-31800</v>
+        <v>69300</v>
       </c>
       <c r="G21" s="3">
+        <v>-32400</v>
+      </c>
+      <c r="H21" s="3">
         <v>43800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>59500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>79300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>81700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>66800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>55000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>53800</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1308,44 +1344,47 @@
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E22" s="3">
         <v>900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>2000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>4100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>2400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>200</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
       <c r="M22" s="3">
         <v>0</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
+      <c r="N22" s="3">
+        <v>0</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>3</v>
@@ -1356,45 +1395,48 @@
       <c r="Q22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>29900</v>
+      </c>
+      <c r="E23" s="3">
         <v>26900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>53400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-73300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>30800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>54400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>90100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>76200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>70000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>50100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>47800</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1404,45 +1446,48 @@
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E24" s="3">
         <v>12200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>16700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-6400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>17700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>16900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>27200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>22200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>28100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>11700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>11500</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1452,9 +1497,12 @@
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1500,45 +1548,48 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>23400</v>
+      </c>
+      <c r="E26" s="3">
         <v>14700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>36700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-66900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>13200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>37500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>62900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>54000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>42000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>38400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>36300</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1548,45 +1599,48 @@
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>23900</v>
+      </c>
+      <c r="E27" s="3">
         <v>15100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>38000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-61600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>14000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>40000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>63600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>54000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>42000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>37000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>33900</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1596,9 +1650,12 @@
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1644,9 +1701,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1692,9 +1752,12 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1740,9 +1803,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1788,45 +1854,48 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>500</v>
+      </c>
+      <c r="E32" s="3">
         <v>2100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>3000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>3300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>3800</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-6700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-6500</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1836,45 +1905,48 @@
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>23800</v>
+      </c>
+      <c r="E33" s="3">
         <v>15100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>38000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-61600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>14000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>40000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>63600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>54000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>42000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>37000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>33900</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1884,9 +1956,12 @@
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1932,45 +2007,48 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>23800</v>
+      </c>
+      <c r="E35" s="3">
         <v>15100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>38000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-61600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>14000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>40000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>63600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>54000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>42000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>37000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>33900</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1980,50 +2058,53 @@
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2033,9 +2114,12 @@
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2054,8 +2138,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2074,44 +2159,45 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>236200</v>
+      </c>
+      <c r="E41" s="3">
         <v>204200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>108000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>101400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>47000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>93600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>45900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>183800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>24900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>124700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>72700</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2121,45 +2207,48 @@
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E42" s="3">
         <v>1800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>64900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>35400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>114400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>83400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>92500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>144400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>167500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>38000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>57200</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2169,45 +2258,48 @@
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>27100</v>
+      </c>
+      <c r="E43" s="3">
         <v>35400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>47900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>114100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>119900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>51100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>30700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>19200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>9800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>25800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>17100</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2217,29 +2309,32 @@
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>700</v>
+      </c>
+      <c r="E44" s="3">
         <v>900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>3200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>600</v>
-      </c>
-      <c r="I44" s="3">
-        <v>400</v>
       </c>
       <c r="J44" s="3">
         <v>400</v>
@@ -2248,13 +2343,13 @@
         <v>400</v>
       </c>
       <c r="L44" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="M44" s="3">
         <v>300</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>3</v>
+      <c r="N44" s="3">
+        <v>300</v>
       </c>
       <c r="O44" s="3" t="s">
         <v>3</v>
@@ -2265,45 +2360,48 @@
       <c r="Q44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E45" s="3">
         <v>6900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>7900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>11900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>9500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>7800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>19600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>33800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>15200</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2313,45 +2411,48 @@
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>271100</v>
+      </c>
+      <c r="E46" s="3">
         <v>251400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>229400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>263100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>288300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>242700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>181700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>356300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>228300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>222600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>162500</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2361,45 +2462,48 @@
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>22400</v>
+      </c>
+      <c r="E47" s="3">
         <v>25200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>26100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>25600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>34400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>131700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>137700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>25000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>18800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>4900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>11700</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2409,45 +2513,48 @@
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>241600</v>
+      </c>
+      <c r="E48" s="3">
         <v>271000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>331500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>370800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>164600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>102400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>88300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>32300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>14900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>15400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>20300</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2457,45 +2564,48 @@
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E49" s="3">
         <v>23500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>41600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>48800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>100900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>90600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>85600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1300</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2505,9 +2615,12 @@
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2553,9 +2666,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2601,45 +2717,48 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>101800</v>
+      </c>
+      <c r="E52" s="3">
         <v>70800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>42000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>56000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>75300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>13600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>14300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>16800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>6300</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2649,9 +2768,12 @@
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2697,45 +2819,48 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>684300</v>
+      </c>
+      <c r="E54" s="3">
         <v>677800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>714500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>824100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>734700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>627200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>548100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>447800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>269900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>260800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>202100</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2745,9 +2870,12 @@
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2766,8 +2894,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2786,34 +2915,35 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E57" s="3">
         <v>8300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>10800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>18200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1300</v>
-      </c>
-      <c r="K57" s="3">
-        <v>1100</v>
       </c>
       <c r="L57" s="3">
         <v>1100</v>
@@ -2821,8 +2951,8 @@
       <c r="M57" s="3">
         <v>1100</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
+      <c r="N57" s="3">
+        <v>1100</v>
       </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
@@ -2833,38 +2963,41 @@
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>34500</v>
+      </c>
+      <c r="E58" s="3">
         <v>33100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>54200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>82800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>63900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>23000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>8600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>8700</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
+      <c r="L58" s="3">
+        <v>0</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
@@ -2878,48 +3011,51 @@
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>93400</v>
+      </c>
+      <c r="E59" s="3">
         <v>85800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>92000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>89500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>96000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>83600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>87000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>78000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>81400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>67300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>51500</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2929,45 +3065,48 @@
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>168800</v>
+      </c>
+      <c r="E60" s="3">
         <v>159700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>189200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>223900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>196800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>133200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>114200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>103200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>101900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>68300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>52500</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2977,27 +3116,30 @@
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>176100</v>
+      </c>
+      <c r="E61" s="3">
         <v>201700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>204300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>243000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>47500</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
       <c r="I61" s="3">
         <v>0</v>
       </c>
@@ -3025,45 +3167,48 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>82300</v>
+      </c>
+      <c r="E62" s="3">
         <v>76900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>69600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>69300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>83400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>66700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>57100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>41700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>32300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>49700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>37900</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3073,9 +3218,12 @@
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3121,9 +3269,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3169,9 +3320,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3217,45 +3371,48 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>454400</v>
+      </c>
+      <c r="E66" s="3">
         <v>473300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>505800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>583600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>413100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>282600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>258300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>206500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>157300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>118100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>90600</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3265,9 +3422,12 @@
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3286,8 +3446,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3333,9 +3494,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3381,9 +3545,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3429,9 +3596,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3477,45 +3647,48 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-41700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-62800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-80200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-118500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>51400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>87300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>44300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>36700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>34300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>77400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>44300</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3525,9 +3698,12 @@
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3573,9 +3749,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3621,9 +3800,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3669,45 +3851,48 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>225400</v>
+      </c>
+      <c r="E76" s="3">
         <v>199900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>203400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>233700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>292400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>322100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>267300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>240000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>112500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>142700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>111500</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3717,9 +3902,12 @@
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3765,50 +3953,53 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3818,45 +4009,48 @@
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>23800</v>
+      </c>
+      <c r="E81" s="3">
         <v>15100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>38000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-61600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>14000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>40000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>63600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>54000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>42000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>37000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>33900</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3866,9 +4060,12 @@
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3887,44 +4084,45 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E83" s="3">
         <v>15200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>15500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>17300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>18000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>9100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>5400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>4900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>6000</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3934,9 +4132,12 @@
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3982,9 +4183,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4030,9 +4234,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4078,9 +4285,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4126,9 +4336,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4174,45 +4387,48 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>40200</v>
+      </c>
+      <c r="E89" s="3">
         <v>51200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>64200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>42700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>59700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>45200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>73800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>80700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>72200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>61700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>51300</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4222,9 +4438,12 @@
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4243,44 +4462,45 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-37300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-10900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-12400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-12100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-91600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-17100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-30600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-20100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1900</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
@@ -4290,9 +4510,12 @@
       <c r="Q91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4338,9 +4561,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4386,45 +4612,48 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="E94" s="3">
         <v>47300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-13200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>61000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-154000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-17100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-175200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-26400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-114500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>10300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-26800</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4434,9 +4663,12 @@
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4455,38 +4687,39 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E96" s="3">
         <v>9700</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
       <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
         <v>5900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>50400</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>32600</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>29200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>89000</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
@@ -4502,9 +4735,12 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4550,9 +4786,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4598,9 +4837,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4646,45 +4888,48 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="E100" s="3">
         <v>1400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-42800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-48600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>37800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>17700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-30500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>96400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-99200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-18500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-7400</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4694,45 +4939,48 @@
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E101" s="3">
         <v>600</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
         <v>200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>9600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>800</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
@@ -4742,45 +4990,48 @@
       <c r="Q101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>21900</v>
+      </c>
+      <c r="E102" s="3">
         <v>100500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>8100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>55200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-56700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>44700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-132900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>160300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-141700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>54300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>17900</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4790,7 +5041,10 @@
       <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
